--- a/data/database/shopgraph_purchase_history.xlsx
+++ b/data/database/shopgraph_purchase_history.xlsx
@@ -30,14 +30,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="mm/dd/yyyy\ hh:mm"/>
     <numFmt numFmtId="166" formatCode="mmm\ yyyy"/>
     <numFmt numFmtId="167" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="168" formatCode="mm/dd/yyyy hh:mm"/>
     <numFmt numFmtId="169" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="170" formatCode="mm/dd/yyyy hh:mm"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -370,7 +369,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -526,7 +525,8 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15709,7 +15709,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr/>
               </a:p>
@@ -21184,7 +21184,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" s="64">
       <c r="A2" s="1">
         <f>SUM(K2,M2,O2,Q2,S2,U2)</f>
         <v/>
@@ -21231,7 +21231,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" s="64">
       <c r="A3" s="1">
         <f>SUM(K3,M3,O3,Q3,S3,U3)</f>
         <v/>
@@ -21278,7 +21278,7 @@
         <v>39.77</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" s="64">
       <c r="A4" s="1">
         <f>SUM(K4,M4,O4,Q4,S4,U4)</f>
         <v/>
@@ -21325,7 +21325,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" s="64">
       <c r="A5" s="1">
         <f>SUM(K5,M5,O5,Q5,S5,U5)</f>
         <v/>
@@ -21372,7 +21372,7 @@
         <v>4.96</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" s="64">
       <c r="A6" s="1">
         <f>SUM(K6,M6,O6,Q6,S6,U6)</f>
         <v/>
@@ -21419,7 +21419,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" s="64">
       <c r="A7" s="1">
         <f>SUM(K7,M7,O7,Q7,S7,U7)</f>
         <v/>
@@ -21466,7 +21466,7 @@
         <v>3.48</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" s="64">
       <c r="A8" s="1">
         <f>SUM(K8,M8,O8,Q8,S8,U8)</f>
         <v/>
@@ -21513,7 +21513,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" s="64">
       <c r="A9" s="1">
         <f>SUM(K9,M9,O9,Q9,S9,U9)</f>
         <v/>
@@ -21560,7 +21560,7 @@
         <v>2.77</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" s="64">
       <c r="A10" s="1">
         <f>SUM(K10,M10,O10,Q10,S10,U10)</f>
         <v/>
@@ -21613,7 +21613,7 @@
         <v>4.48</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" s="64">
       <c r="A11" s="1">
         <f>SUM(K11,M11,O11,Q11,S11,U11)</f>
         <v/>
@@ -21666,7 +21666,7 @@
         <v>6.96</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" s="64">
       <c r="A12" s="1">
         <f>SUM(K12,M12,O12,Q12,S12,U12)</f>
         <v/>
@@ -21719,7 +21719,7 @@
         <v>8.369999999999999</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" s="64">
       <c r="A13" s="1">
         <f>SUM(K13,M13,O13,Q13,S13,U13)</f>
         <v/>
@@ -21772,7 +21772,7 @@
         <v>23.94</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" s="64">
       <c r="A14" s="1">
         <f>SUM(K14,M14,O14,Q14,S14,U14)</f>
         <v/>
@@ -21825,7 +21825,7 @@
         <v>3.16</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" s="64">
       <c r="A15" s="1">
         <f>SUM(K15,M15,O15,Q15,S15,U15)</f>
         <v/>
@@ -21878,7 +21878,7 @@
         <v>5.82</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" s="64">
       <c r="A16" s="1">
         <f>SUM(K16,M16,O16,Q16,S16,U16)</f>
         <v/>
@@ -21931,7 +21931,7 @@
         <v>7.97</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" s="64">
       <c r="A17" s="1">
         <f>SUM(K17,M17,O17,Q17,S17,U17)</f>
         <v/>
@@ -21984,7 +21984,7 @@
         <v>5.32</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" s="64">
       <c r="A18" s="1">
         <f>SUM(K18,M18,O18,Q18,S18,U18)</f>
         <v/>
@@ -22037,7 +22037,7 @@
         <v>4.97</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" s="64">
       <c r="A19" s="1">
         <f>SUM(K19,M19,O19,Q19,S19,U19)</f>
         <v/>
@@ -22090,7 +22090,7 @@
         <v>4.97</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" s="64">
       <c r="A20" s="1">
         <f>SUM(K20,M20,O20,Q20,S20,U20)</f>
         <v/>
@@ -22143,7 +22143,7 @@
         <v>4.88</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" s="64">
       <c r="A21" s="1">
         <f>SUM(K21,M21,O21,Q21,S21,U21)</f>
         <v/>
@@ -22196,7 +22196,7 @@
         <v>9.67</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" s="64">
       <c r="A22" s="1">
         <f>SUM(K22,M22,O22,Q22,S22,U22)</f>
         <v/>
@@ -22249,7 +22249,7 @@
         <v>7.96</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" s="64">
       <c r="A23" s="1">
         <f>SUM(K23,M23,O23,Q23,S23,U23)</f>
         <v/>
@@ -22302,7 +22302,7 @@
         <v>4.97</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" s="64">
       <c r="A24" s="1">
         <f>SUM(K24,M24,O24,Q24,S24,U24)</f>
         <v/>
@@ -22361,7 +22361,7 @@
         <v>1.83</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" s="64">
       <c r="A25" s="1">
         <f>SUM(K25,M25,O25,Q25,S25,U25)</f>
         <v/>
@@ -22414,7 +22414,7 @@
         <v>9.98</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" s="64">
       <c r="A26" s="1">
         <f>SUM(K26,M26,O26,Q26,S26,U26)</f>
         <v/>
@@ -22461,7 +22461,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" s="64">
       <c r="A27" s="1">
         <f>SUM(K27,M27,O27,Q27,S27,U27)</f>
         <v/>
@@ -22508,7 +22508,7 @@
         <v>39.77</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" s="64">
       <c r="A28" s="1">
         <f>SUM(K28,M28,O28,Q28,S28,U28)</f>
         <v/>
@@ -22555,7 +22555,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" s="64">
       <c r="A29" s="1">
         <f>SUM(K29,M29,O29,Q29,S29,U29)</f>
         <v/>
@@ -22602,7 +22602,7 @@
         <v>4.96</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" s="64">
       <c r="A30" s="1">
         <f>SUM(K30,M30,O30,Q30,S30,U30)</f>
         <v/>
@@ -22649,7 +22649,7 @@
         <v>11.76</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" s="64">
       <c r="A31" s="1">
         <f>SUM(K31,M31,O31,Q31,S31,U31)</f>
         <v/>
@@ -22696,7 +22696,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" s="64">
       <c r="A32" s="1">
         <f>SUM(K32,M32,O32,Q32,S32,U32)</f>
         <v/>
@@ -22743,7 +22743,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" s="64">
       <c r="A33" s="1">
         <f>SUM(K33,M33,O33,Q33,S33,U33)</f>
         <v/>
@@ -22790,7 +22790,7 @@
         <v>5.97</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" s="64">
       <c r="A34" s="1">
         <f>SUM(K34,M34,O34,Q34,S34,U34)</f>
         <v/>
@@ -22837,7 +22837,7 @@
         <v>6.88</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" s="64">
       <c r="A35" s="1">
         <f>SUM(K35,M35,O35,Q35,S35,U35)</f>
         <v/>
@@ -22884,7 +22884,7 @@
         <v>6.48</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" s="64">
       <c r="A36" s="1">
         <f>SUM(K36,M36,O36,Q36,S36,U36)</f>
         <v/>
@@ -22931,7 +22931,7 @@
         <v>5.74</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" s="64">
       <c r="A37" s="1">
         <f>SUM(K37,M37,O37,Q37,S37,U37)</f>
         <v/>
@@ -22978,7 +22978,7 @@
         <v>5.98</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" s="64">
       <c r="A38" s="1">
         <f>SUM(K38,M38,O38,Q38,S38,U38)</f>
         <v/>
@@ -23025,7 +23025,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" s="64">
       <c r="A39" s="1">
         <f>SUM(K39,M39,O39,Q39,S39,U39)</f>
         <v/>
@@ -23072,7 +23072,7 @@
         <v>11.93</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" s="64">
       <c r="A40" s="1">
         <f>SUM(K40,M40,O40,Q40,S40,U40)</f>
         <v/>
@@ -23119,7 +23119,7 @@
         <v>7.98</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" s="64">
       <c r="A41" s="1">
         <f>SUM(K41,M41,O41,Q41,S41,U41)</f>
         <v/>
@@ -23166,7 +23166,7 @@
         <v>6.48</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" s="64">
       <c r="A42" s="1">
         <f>SUM(K42,M42,O42,Q42,S42,U42)</f>
         <v/>
@@ -23213,7 +23213,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" s="64">
       <c r="A43" s="1">
         <f>SUM(K43,M43,O43,Q43,S43,U43)</f>
         <v/>
@@ -23260,7 +23260,7 @@
         <v>3.16</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" s="64">
       <c r="A44" s="1">
         <f>SUM(K44,M44,O44,Q44,S44,U44)</f>
         <v/>
@@ -23313,7 +23313,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" s="64">
       <c r="A45" s="1">
         <f>SUM(K45,M45,O45,Q45,S45,U45)</f>
         <v/>
@@ -23366,7 +23366,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" s="64">
       <c r="A46" s="1">
         <f>SUM(K46,M46,O46,Q46,S46,U46)</f>
         <v/>
@@ -23419,7 +23419,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" s="64">
       <c r="A47" s="1">
         <f>SUM(K47,M47,O47,Q47,S47,U47)</f>
         <v/>
@@ -23466,7 +23466,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" s="64">
       <c r="A48" s="1">
         <f>SUM(K48,M48,O48,Q48,S48,U48)</f>
         <v/>
@@ -23519,7 +23519,7 @@
         <v>1.76</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" s="64">
       <c r="A49" s="1">
         <f>SUM(K49,M49,O49,Q49,S49,U49)</f>
         <v/>
@@ -23566,7 +23566,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" s="64">
       <c r="A50" s="1">
         <f>SUM(K50,M50,O50,Q50,S50,U50)</f>
         <v/>
@@ -23613,7 +23613,7 @@
         <v>2.52</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" s="64">
       <c r="A51" s="1">
         <f>SUM(K51,M51,O51,Q51,S51,U51)</f>
         <v/>
@@ -23660,7 +23660,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" s="64">
       <c r="A52" s="1">
         <f>SUM(K52,M52,O52,Q52,S52,U52)</f>
         <v/>
@@ -23707,7 +23707,7 @@
         <v>3.29</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" s="64">
       <c r="A53" s="1">
         <f>SUM(K53,M53,O53,Q53,S53,U53)</f>
         <v/>
@@ -23754,7 +23754,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" s="64">
       <c r="A54" s="1">
         <f>SUM(K54,M54,O54,Q54,S54,U54)</f>
         <v/>
@@ -23801,7 +23801,7 @@
         <v>3.41</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" s="64">
       <c r="A55" s="1">
         <f>SUM(K55,M55,O55,Q55,S55,U55)</f>
         <v/>
@@ -23848,7 +23848,7 @@
         <v>2.99</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" s="64">
       <c r="A56" s="1">
         <f>SUM(K56,M56,O56,Q56,S56,U56)</f>
         <v/>
@@ -23895,7 +23895,7 @@
         <v>8.289999999999999</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" s="64">
       <c r="A57" s="1">
         <f>SUM(K57,M57,O57,Q57,S57,U57)</f>
         <v/>
@@ -23942,7 +23942,7 @@
         <v>2.69</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" s="64">
       <c r="A58" s="1">
         <f>SUM(K58,M58,O58,Q58,S58,U58)</f>
         <v/>
@@ -23989,7 +23989,7 @@
         <v>3.69</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" s="64">
       <c r="A59" s="1">
         <f>SUM(K59,M59,O59,Q59,S59,U59)</f>
         <v/>
@@ -24036,7 +24036,7 @@
         <v>1.29</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" s="64">
       <c r="A60" s="1">
         <f>SUM(K60,M60,O60,Q60,S60,U60)</f>
         <v/>
@@ -24083,7 +24083,7 @@
         <v>3.89</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" s="64">
       <c r="A61" s="1">
         <f>SUM(K61,M61,O61,Q61,S61,U61)</f>
         <v/>
@@ -24130,7 +24130,7 @@
         <v>2.59</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" s="64">
       <c r="A62" s="1">
         <f>SUM(K62,M62,O62,Q62,S62,U62)</f>
         <v/>
@@ -24177,7 +24177,7 @@
         <v>4.39</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" s="64">
       <c r="A63" s="1">
         <f>SUM(K63,M63,O63,Q63,S63,U63)</f>
         <v/>
@@ -24224,7 +24224,7 @@
         <v>3.45</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" s="64">
       <c r="A64" s="1">
         <f>SUM(K64,M64,O64,Q64,S64,U64)</f>
         <v/>
@@ -24271,7 +24271,7 @@
         <v>2.39</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" s="64">
       <c r="A65" s="1">
         <f>SUM(K65,M65,O65,Q65,S65,U65)</f>
         <v/>
@@ -24318,7 +24318,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" s="64">
       <c r="A66" s="1">
         <f>SUM(K66,M66,O66,Q66,S66,U66)</f>
         <v/>
@@ -24371,7 +24371,7 @@
         <v>1.99</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" s="64">
       <c r="A67" s="1">
         <f>SUM(K67,M67,O67,Q67,S67,U67)</f>
         <v/>
@@ -24418,7 +24418,7 @@
         <v>2.49</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" s="64">
       <c r="A68" s="1">
         <f>SUM(K68,M68,O68,Q68,S68,U68)</f>
         <v/>
@@ -24471,7 +24471,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" s="64">
       <c r="A69" s="1">
         <f>SUM(K69,M69,O69,Q69,S69,U69)</f>
         <v/>
@@ -24524,7 +24524,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" s="64">
       <c r="A70" s="1">
         <f>SUM(K70,M70,O70,Q70,S70,U70)</f>
         <v/>
@@ -24571,7 +24571,7 @@
         <v>2.99</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" s="64">
       <c r="A71" s="1">
         <f>SUM(K71,M71,O71,Q71,S71,U71)</f>
         <v/>
@@ -24618,7 +24618,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" s="64">
       <c r="A72" s="1">
         <f>SUM(K72,M72,O72,Q72,S72,U72)</f>
         <v/>
@@ -24665,7 +24665,7 @@
         <v>1.99</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" s="64">
       <c r="A73" s="1">
         <f>SUM(K73,M73,O73,Q73,S73,U73)</f>
         <v/>
@@ -24712,7 +24712,7 @@
         <v>5.25</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" s="64">
       <c r="A74" s="1">
         <f>SUM(K74,M74,O74,Q74,S74,U74)</f>
         <v/>
@@ -24759,7 +24759,7 @@
         <v>3.37</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" s="64">
       <c r="A75" s="1">
         <f>SUM(K75,M75,O75,Q75,S75,U75)</f>
         <v/>
@@ -24806,7 +24806,7 @@
         <v>5.99</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" s="64">
       <c r="A76" s="1">
         <f>SUM(K76,M76,O76,Q76,S76,U76)</f>
         <v/>
@@ -24853,7 +24853,7 @@
         <v>2.79</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" s="64">
       <c r="A77" s="1">
         <f>SUM(K77,M77,O77,Q77,S77,U77)</f>
         <v/>
@@ -24900,7 +24900,7 @@
         <v>1.99</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" s="64">
       <c r="A78" s="1">
         <f>SUM(K78,M78,O78,Q78,S78,U78)</f>
         <v/>
@@ -24947,7 +24947,7 @@
         <v>2.89</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" s="64">
       <c r="A79" s="1">
         <f>SUM(K79,M79,O79,Q79,S79,U79)</f>
         <v/>
@@ -24994,7 +24994,7 @@
         <v>5.99</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" s="64">
       <c r="A80" s="1">
         <f>SUM(K80,M80,O80,Q80,S80,U80)</f>
         <v/>
@@ -25041,7 +25041,7 @@
         <v>3.99</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" s="64">
       <c r="A81" s="1">
         <f>SUM(K81,M81,O81,Q81,S81,U81)</f>
         <v/>
@@ -25088,7 +25088,7 @@
         <v>3.29</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" s="64">
       <c r="A82" s="1">
         <f>SUM(K82,M82,O82,Q82,S82,U82)</f>
         <v/>
@@ -25135,7 +25135,7 @@
         <v>2.99</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" s="64">
       <c r="A83" s="1">
         <f>SUM(K83,M83,O83,Q83,S83,U83)</f>
         <v/>
@@ -25182,7 +25182,7 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" s="64">
       <c r="A84" s="1">
         <f>SUM(K84,M84,O84,Q84,S84,U84)</f>
         <v/>
@@ -25229,7 +25229,7 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" s="64">
       <c r="A85" s="1">
         <f>SUM(K85,M85,O85,Q85,S85,U85)</f>
         <v/>
@@ -25276,14 +25276,14 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" s="64">
       <c r="A86" s="1">
         <f>SUM(K86,M86,O86,Q86,S86,U86)</f>
         <v/>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -25293,56 +25293,68 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Vans Waffle Blueberry Gf</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Van's Gluten Free Blueberry Waffles</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Frozen Breakfast</t>
+          <t>Fees &amp; Charges</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>46259</v>
+        <v>46240</v>
       </c>
       <c r="K86" s="1" t="n">
-        <v>3.89</v>
+        <v>3.48</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>46259</v>
+        <v>46241</v>
       </c>
       <c r="M86" s="1" t="n">
-        <v>3.89</v>
+        <v>3.48</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>46299</v>
+        <v>46247</v>
       </c>
       <c r="O86" s="1" t="n">
-        <v>3.89</v>
-      </c>
-    </row>
-    <row r="87">
+        <v>1.76</v>
+      </c>
+      <c r="P86" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="Q86" s="1" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="R86" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="S86" s="1" t="n">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="87" s="64">
       <c r="A87" s="1">
         <f>SUM(K87,M87,O87,Q87,S87,U87)</f>
         <v/>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -25352,43 +25364,49 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Chobani 4Pk Hero Batch</t>
+          <t>Driver tip</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Chobani Greek Yogurt 4-Pack, Hero Batch</t>
+          <t>Driver Tip</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Yogurt</t>
+          <t>Fees &amp; Charges</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>46259</v>
+        <v>46240</v>
       </c>
       <c r="K87" s="1" t="n">
-        <v>5.65</v>
+        <v>16.92</v>
       </c>
       <c r="L87" s="2" t="n">
-        <v>46299</v>
+        <v>46247</v>
       </c>
       <c r="M87" s="1" t="n">
-        <v>5.65</v>
-      </c>
-    </row>
-    <row r="88">
+        <v>17.72</v>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="O87" s="1" t="n">
+        <v>12.14</v>
+      </c>
+    </row>
+    <row r="88" s="64">
       <c r="A88" s="1">
         <f>SUM(K88,M88,O88,Q88,S88,U88)</f>
         <v/>
@@ -25405,7 +25423,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Command Heavy Duty Picture Hangers, Hold 20 tbs, Black, Damage-Free Hanging, 8 Pairs Adhesive Strips</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -25420,46 +25438,22 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Command Heavy Duty Picture Hangers</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Fees &amp; Charges</t>
+          <t>Home Improvement</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>46240</v>
+        <v>46260</v>
       </c>
       <c r="K88" s="1" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="L88" s="2" t="n">
-        <v>46241</v>
-      </c>
-      <c r="M88" s="1" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="N88" s="2" t="n">
-        <v>46247</v>
-      </c>
-      <c r="O88" s="1" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="P88" s="2" t="n">
-        <v>46260</v>
-      </c>
-      <c r="Q88" s="1" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="R88" s="2" t="n">
-        <v>46260</v>
-      </c>
-      <c r="S88" s="1" t="n">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="89">
+        <v>28.54</v>
+      </c>
+    </row>
+    <row r="89" s="64">
       <c r="A89" s="1">
         <f>SUM(K89,M89,O89,Q89,S89,U89)</f>
         <v/>
@@ -25476,7 +25470,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Driver tip</t>
+          <t>Dove Men+Care Antiperspirant Deodorant Stick 72-Hour Sweat &amp; Odor Protection Clean Comfort Antiperspirant For Men</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -25491,34 +25485,24 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Driver Tip</t>
+          <t>Dove Men+Care Antiperspirant</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Fees &amp; Charges</t>
+          <t>Deodorant</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>46240</v>
-      </c>
-      <c r="K89" s="1" t="n">
-        <v>16.92</v>
-      </c>
-      <c r="L89" s="2" t="n">
-        <v>46247</v>
-      </c>
-      <c r="M89" s="1" t="n">
-        <v>17.72</v>
-      </c>
-      <c r="N89" s="2" t="n">
         <v>46260</v>
       </c>
-      <c r="O89" s="1" t="n">
-        <v>12.14</v>
-      </c>
-    </row>
-    <row r="90">
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" s="64">
       <c r="A90" s="1">
         <f>SUM(K90,M90,O90,Q90,S90,U90)</f>
         <v/>
@@ -25535,7 +25519,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Command Heavy Duty Picture Hangers, Hold 20 tbs, Black, Damage-Free Hanging, 8 Pairs Adhesive Strips</t>
+          <t>Dawn Ultra 11" Puff Glassware and Dish Cleaning Brush Wand with Sponge Head</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -25550,22 +25534,22 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Command Heavy Duty Picture Hangers</t>
+          <t>Dawn Dish Cleaning Brush Wand</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Dishwashing Supplies</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
         <v>46260</v>
       </c>
       <c r="K90" s="1" t="n">
-        <v>28.54</v>
-      </c>
-    </row>
-    <row r="91">
+        <v>4.46</v>
+      </c>
+    </row>
+    <row r="91" s="64">
       <c r="A91" s="1">
         <f>SUM(K91,M91,O91,Q91,S91,U91)</f>
         <v/>
@@ -25582,7 +25566,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Dove Men+Care Antiperspirant Deodorant Stick 72-Hour Sweat &amp; Odor Protection Clean Comfort Antiperspirant For Men</t>
+          <t>Once Upon a Farm Organic Tractor Wheels Toddler Bar, Apple, Sweet Potato &amp; Spinach, 10ct</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -25597,24 +25581,22 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Dove Men+Care Antiperspirant</t>
+          <t>Once Upon a Farm Tractor Wheels Toddler Bars</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Deodorant</t>
+          <t>Baby &amp; Toddler Food</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
         <v>46260</v>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
+      <c r="K91" s="1" t="n">
+        <v>9.98</v>
+      </c>
+    </row>
+    <row r="92" s="64">
       <c r="A92" s="1">
         <f>SUM(K92,M92,O92,Q92,S92,U92)</f>
         <v/>
@@ -25631,7 +25613,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Dawn Ultra 11" Puff Glassware and Dish Cleaning Brush Wand with Sponge Head</t>
+          <t>Weiman Granite &amp; Stone Disinfectant Cleaner &amp; Polish, 24 floz</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -25646,22 +25628,22 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Dawn Dish Cleaning Brush Wand</t>
+          <t>Weiman Granite &amp; Stone Cleaner &amp; Polish</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Dishwashing Supplies</t>
+          <t>Household Cleaners</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
         <v>46260</v>
       </c>
       <c r="K92" s="1" t="n">
-        <v>4.46</v>
-      </c>
-    </row>
-    <row r="93">
+        <v>6.24</v>
+      </c>
+    </row>
+    <row r="93" s="64">
       <c r="A93" s="1">
         <f>SUM(K93,M93,O93,Q93,S93,U93)</f>
         <v/>
@@ -25678,7 +25660,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Once Upon a Farm Organic Tractor Wheels Toddler Bar, Apple, Sweet Potato &amp; Spinach, 10ct</t>
+          <t>Chobani Low-Fat Vanilla Greek Yogurt Mixed Berry On The Bottom, Hero Batch z 4PK</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -25693,22 +25675,22 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Once Upon a Farm Tractor Wheels Toddler Bars</t>
+          <t>Chobani Vanilla Mixed Berry Greek Yogurt</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Baby &amp; Toddler Food</t>
+          <t>Yogurt</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
         <v>46260</v>
       </c>
       <c r="K93" s="1" t="n">
-        <v>9.98</v>
-      </c>
-    </row>
-    <row r="94">
+        <v>4.67</v>
+      </c>
+    </row>
+    <row r="94" s="64">
       <c r="A94" s="1">
         <f>SUM(K94,M94,O94,Q94,S94,U94)</f>
         <v/>
@@ -25725,7 +25707,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Weiman Granite &amp; Stone Disinfectant Cleaner &amp; Polish, 24 floz</t>
+          <t>Fresh Banana, Each 4 weight adjusted aty4</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -25740,29 +25722,35 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Weiman Granite &amp; Stone Cleaner &amp; Polish</t>
+          <t>Bananas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Household Cleaners</t>
+          <t>Fresh Fruit</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
         <v>46260</v>
       </c>
       <c r="K94" s="1" t="n">
-        <v>6.24</v>
-      </c>
-    </row>
-    <row r="95">
+        <v>0.6</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="M94" s="1" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="95" s="64">
       <c r="A95" s="1">
         <f>SUM(K95,M95,O95,Q95,S95,U95)</f>
         <v/>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Honey Pineapple</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -25772,7 +25760,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chobani Low-Fat Vanilla Greek Yogurt Mixed Berry On The Bottom, Hero Batch z 4PK</t>
+          <t>1 Caramel Macchiato</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -25782,34 +25770,34 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Chobani Vanilla Mixed Berry Greek Yogurt</t>
+          <t>1 Caramel Macchiato</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Yogurt</t>
+          <t>Prepared Coffee</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="K95" s="1" t="n">
-        <v>4.67</v>
-      </c>
-    </row>
-    <row r="96">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="96" s="64">
       <c r="A96" s="1">
         <f>SUM(K96,M96,O96,Q96,S96,U96)</f>
         <v/>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Honey Pineapple</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -25819,7 +25807,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Fresh Banana, Each 4 weight adjusted aty4</t>
+          <t>1 Iced Caramel Macchiato</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -25829,33 +25817,27 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Bananas</t>
+          <t>1 Iced Caramel Macchiato</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Fresh Fruit</t>
+          <t>Prepared Coffee</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="K96" s="1" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L96" s="2" t="n">
-        <v>46260</v>
-      </c>
-      <c r="M96" s="1" t="n">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="97">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="97" s="64">
       <c r="A97" s="1">
         <f>SUM(K97,M97,O97,Q97,S97,U97)</f>
         <v/>
@@ -25872,37 +25854,37 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1 Caramel Macchiato</t>
+          <t>1 Frenchy Plate</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
+          <t>LF</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>1 Caramel Macchiato</t>
+          <t>1 Frenchy Plate</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Prepared Coffee</t>
+          <t>Prepared Meals</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
         <v>46261</v>
       </c>
       <c r="K97" s="1" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="98">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="98" s="64">
       <c r="A98" s="1">
         <f>SUM(K98,M98,O98,Q98,S98,U98)</f>
         <v/>
@@ -25919,37 +25901,37 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1 Iced Caramel Macchiato</t>
+          <t>1 Chicken N French Toast</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1 Iced Caramel Macchiato</t>
+          <t>1 Chicken N French Toast</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Prepared Coffee</t>
+          <t>Prepared Meals</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
         <v>46261</v>
       </c>
       <c r="K98" s="1" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="99">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="99" s="64">
       <c r="A99" s="1">
         <f>SUM(K99,M99,O99,Q99,S99,U99)</f>
         <v/>
@@ -25966,12 +25948,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1 Frenchy Plate</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -25981,22 +25963,22 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1 Frenchy Plate</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Prepared Meals</t>
+          <t>Fees &amp; Charges</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
         <v>46261</v>
       </c>
       <c r="K99" s="1" t="n">
-        <v>14.9</v>
-      </c>
-    </row>
-    <row r="100">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="100" s="64">
       <c r="A100" s="1">
         <f>SUM(K100,M100,O100,Q100,S100,U100)</f>
         <v/>
@@ -26013,12 +25995,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1 Chicken N French Toast</t>
+          <t>Tip</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -26028,29 +26010,29 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>1 Chicken N French Toast</t>
+          <t>Tip</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Prepared Meals</t>
+          <t>Fees &amp; Charges</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
         <v>46261</v>
       </c>
       <c r="K100" s="1" t="n">
-        <v>16.3</v>
-      </c>
-    </row>
-    <row r="101">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="101" s="64">
       <c r="A101" s="1">
         <f>SUM(K101,M101,O101,Q101,S101,U101)</f>
         <v/>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Honey Pineapple</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -26060,44 +26042,44 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Jif Nsa P/B Creamy</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Jif No Sugar Added Creamy Peanut Butter</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Fees &amp; Charges</t>
+          <t>Peanut Butter</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="K101" s="1" t="n">
-        <v>2.96</v>
-      </c>
-    </row>
-    <row r="102">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="102" s="64">
       <c r="A102" s="1">
         <f>SUM(K102,M102,O102,Q102,S102,U102)</f>
         <v/>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Honey Pineapple</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -26107,37 +26089,37 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Tip</t>
+          <t>King Arth G/ Pnck Hix</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Tip</t>
+          <t>King Arthur Gluten-Free Pancake Mix</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Fees &amp; Charges</t>
+          <t>Baking Mixes</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="K102" s="1" t="n">
-        <v>2.96</v>
-      </c>
-    </row>
-    <row r="103">
+        <v>5.15</v>
+      </c>
+    </row>
+    <row r="103" s="64">
       <c r="A103" s="1">
         <f>SUM(K103,M103,O103,Q103,S103,U103)</f>
         <v/>
@@ -26154,7 +26136,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Jif Nsa P/B Creamy</t>
+          <t>Bagged Green Beans</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -26169,22 +26151,22 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Jif No Sugar Added Creamy Peanut Butter</t>
+          <t>Green Beans</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Peanut Butter</t>
+          <t>Fresh Vegetables</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="K103" s="1" t="n">
-        <v>3.69</v>
-      </c>
-    </row>
-    <row r="104">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="104" s="64">
       <c r="A104" s="1">
         <f>SUM(K104,M104,O104,Q104,S104,U104)</f>
         <v/>
@@ -26201,7 +26183,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>King Arth G/ Pnck Hix</t>
+          <t>Potato Nibbles Ruby Sensa</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -26216,12 +26198,12 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>King Arthur Gluten-Free Pancake Mix</t>
+          <t>Ruby Sensation Potato Nibbles</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Baking Mixes</t>
+          <t>Fresh Vegetables</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
@@ -26231,7 +26213,7 @@
         <v>5.15</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" s="64">
       <c r="A105" s="1">
         <f>SUM(K105,M105,O105,Q105,S105,U105)</f>
         <v/>
@@ -26248,7 +26230,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bagged Green Beans</t>
+          <t>Cholula Cremosa Gltro Lme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -26263,22 +26245,22 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Green Beans</t>
+          <t>Cholula Cremosa Cilantro Lime Sauce</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Fresh Vegetables</t>
+          <t>Sauces &amp; Condiments</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="K105" s="1" t="n">
-        <v>2.99</v>
-      </c>
-    </row>
-    <row r="106">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="106" s="64">
       <c r="A106" s="1">
         <f>SUM(K106,M106,O106,Q106,S106,U106)</f>
         <v/>
@@ -26295,7 +26277,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Potato Nibbles Ruby Sensa</t>
+          <t>Mc Sig Evrythng Bgel Ssng</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -26310,22 +26292,22 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Ruby Sensation Potato Nibbles</t>
+          <t>McCormick Everything Bagel Seasoning</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Fresh Vegetables</t>
+          <t>Seasonings &amp; Spices</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="K106" s="1" t="n">
-        <v>5.15</v>
-      </c>
-    </row>
-    <row r="107">
+        <v>6.79</v>
+      </c>
+    </row>
+    <row r="107" s="64">
       <c r="A107" s="1">
         <f>SUM(K107,M107,O107,Q107,S107,U107)</f>
         <v/>
@@ -26342,7 +26324,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cholula Cremosa Gltro Lme</t>
+          <t>Banza White Cheddar Shel</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -26357,22 +26339,22 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Cholula Cremosa Cilantro Lime Sauce</t>
+          <t>Banza White Cheddar Shells</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Sauces &amp; Condiments</t>
+          <t>Macaroni &amp; Cheese</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="K107" s="1" t="n">
-        <v>3.19</v>
-      </c>
-    </row>
-    <row r="108">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="108" s="64">
       <c r="A108" s="1">
         <f>SUM(K108,M108,O108,Q108,S108,U108)</f>
         <v/>
@@ -26389,7 +26371,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Mc Sig Evrythng Bgel Ssng</t>
+          <t>anza White Cheddar Shel</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -26404,22 +26386,22 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>McCormick Everything Bagel Seasoning</t>
+          <t>Banza White Cheddar Shells</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Seasonings &amp; Spices</t>
+          <t>Macaroni &amp; Cheese</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="K108" s="1" t="n">
-        <v>6.79</v>
-      </c>
-    </row>
-    <row r="109">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="109" s="64">
       <c r="A109" s="1">
         <f>SUM(K109,M109,O109,Q109,S109,U109)</f>
         <v/>
@@ -26436,7 +26418,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Banza White Cheddar Shel</t>
+          <t>Annie's Dlx Shi&amp;Chd Gf</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -26451,7 +26433,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Banza White Cheddar Shells</t>
+          <t>Annie's Gluten-Free Deluxe Shells &amp; Cheddar</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -26463,10 +26445,10 @@
         <v>46262</v>
       </c>
       <c r="K109" s="1" t="n">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="110">
+        <v>5.45</v>
+      </c>
+    </row>
+    <row r="110" s="64">
       <c r="A110" s="1">
         <f>SUM(K110,M110,O110,Q110,S110,U110)</f>
         <v/>
@@ -26483,7 +26465,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>anza White Cheddar Shel</t>
+          <t>Annie's Dlx Shl&amp;Chd Gf</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -26498,7 +26480,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Banza White Cheddar Shells</t>
+          <t>Annie's Gluten-Free Deluxe Shells &amp; Cheddar</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -26510,10 +26492,10 @@
         <v>46262</v>
       </c>
       <c r="K110" s="1" t="n">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="111">
+        <v>5.45</v>
+      </c>
+    </row>
+    <row r="111" s="64">
       <c r="A111" s="1">
         <f>SUM(K111,M111,O111,Q111,S111,U111)</f>
         <v/>
@@ -26530,7 +26512,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Annie's Dlx Shi&amp;Chd Gf</t>
+          <t>Gw Keta Salmon Fillet</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -26545,22 +26527,22 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Annie's Gluten-Free Deluxe Shells &amp; Cheddar</t>
+          <t>GreenWise Keta Salmon Fillet</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Macaroni &amp; Cheese</t>
+          <t>Fresh Seafood</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="K111" s="1" t="n">
-        <v>5.45</v>
-      </c>
-    </row>
-    <row r="112">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="112" s="64">
       <c r="A112" s="1">
         <f>SUM(K112,M112,O112,Q112,S112,U112)</f>
         <v/>
@@ -26577,7 +26559,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Annie's Dlx Shl&amp;Chd Gf</t>
+          <t>Daiya Shreds Mexican Bld</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -26592,22 +26574,28 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Annie's Gluten-Free Deluxe Shells &amp; Cheddar</t>
+          <t>Daiya Mexican Blend Shreds</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Macaroni &amp; Cheese</t>
+          <t>Plant-Based Cheese</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="K112" s="1" t="n">
-        <v>5.45</v>
-      </c>
-    </row>
-    <row r="113">
+        <v>5.65</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>46262</v>
+      </c>
+      <c r="M112" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" s="64">
       <c r="A113" s="1">
         <f>SUM(K113,M113,O113,Q113,S113,U113)</f>
         <v/>
@@ -26624,12 +26612,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Gw Keta Salmon Fillet</t>
+          <t>Tf Caesar Salad Kit Chop F</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -26639,22 +26627,22 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>GreenWise Keta Salmon Fillet</t>
+          <t>Taylor Farms Chopped Caesar Salad Kit</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Fresh Seafood</t>
+          <t>Salad Kits</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
         <v>46262</v>
       </c>
-      <c r="K113" s="1" t="n">
-        <v>14.29</v>
-      </c>
-    </row>
-    <row r="114">
+      <c r="K113" t="n">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="114" s="64">
       <c r="A114" s="1">
         <f>SUM(K114,M114,O114,Q114,S114,U114)</f>
         <v/>
@@ -26671,12 +26659,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Daiya Shreds Mexican Bld</t>
+          <t>Tf Everything Salad Chop</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>TF</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -26686,28 +26674,22 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Daiya Mexican Blend Shreds</t>
+          <t>Taylor Farms Everything Chopped Salad Kit</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Plant-Based Cheese</t>
+          <t>Salad Kits</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
         <v>46262</v>
       </c>
-      <c r="K114" s="1" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="L114" s="2" t="n">
-        <v>46262</v>
-      </c>
-      <c r="M114" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115">
+      <c r="K114" t="n">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="115" s="64">
       <c r="A115" s="1">
         <f>SUM(K115,M115,O115,Q115,S115,U115)</f>
         <v/>
@@ -26724,12 +26706,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Tf Caesar Salad Kit Chop F</t>
+          <t>Hagen David Blackberry</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>T</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -26739,22 +26721,22 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Taylor Farms Chopped Caesar Salad Kit</t>
+          <t>Häagen-Dazs Blackberry Ice Cream</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Salad Kits</t>
+          <t>Wine</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
         <v>46262</v>
       </c>
-      <c r="K115" t="n">
-        <v>3.33</v>
-      </c>
-    </row>
-    <row r="116">
+      <c r="K115" s="1" t="n">
+        <v>7.19</v>
+      </c>
+    </row>
+    <row r="116" s="64">
       <c r="A116" s="1">
         <f>SUM(K116,M116,O116,Q116,S116,U116)</f>
         <v/>
@@ -26771,12 +26753,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Tf Everything Salad Chop</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>TF</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -26786,22 +26768,22 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Taylor Farms Everything Chopped Salad Kit</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Salad Kits</t>
+          <t>Fees &amp; Charges</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="K116" t="n">
-        <v>3.33</v>
-      </c>
-    </row>
-    <row r="117">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="117" s="64">
       <c r="A117" s="1">
         <f>SUM(K117,M117,O117,Q117,S117,U117)</f>
         <v/>
@@ -26818,12 +26800,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Hagen David Blackberry</t>
+          <t>Tf Everything Salad Chop</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>TF</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -26833,22 +26815,22 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Häagen-Dazs Blackberry Ice Cream</t>
+          <t>Taylor Farms Everything Chopped Salad Kit</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Wine</t>
+          <t>Salad Kits</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
         <v>46262</v>
       </c>
-      <c r="K117" s="1" t="n">
-        <v>7.19</v>
-      </c>
-    </row>
-    <row r="118">
+      <c r="K117" t="n">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="118" s="64">
       <c r="A118" s="1">
         <f>SUM(K118,M118,O118,Q118,S118,U118)</f>
         <v/>
@@ -26865,7 +26847,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Bananas</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -26880,22 +26862,30 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Bananas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Fees &amp; Charges</t>
+          <t>Fresh Fruit</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="K118" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="119">
+        <v>1.53</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" s="64">
       <c r="A119" s="1">
         <f>SUM(K119,M119,O119,Q119,S119,U119)</f>
         <v/>
@@ -26912,12 +26902,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Tf Everything Salad Chop</t>
+          <t>Sweet Loren's Gf Brownie</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>TF</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -26927,22 +26917,22 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Taylor Farms Everything Chopped Salad Kit</t>
+          <t>Sweet Loren's Gluten Free Brownie Cookie Dough</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Salad Kits</t>
+          <t>Refrigerated Dough</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>46262</v>
-      </c>
-      <c r="K119" t="n">
-        <v>3.34</v>
-      </c>
-    </row>
-    <row r="120">
+        <v>46268</v>
+      </c>
+      <c r="K119" s="1" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="120" s="64">
       <c r="A120" s="1">
         <f>SUM(K120,M120,O120,Q120,S120,U120)</f>
         <v/>
@@ -26959,12 +26949,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bananas</t>
+          <t>Publix Half&amp;Half Hg</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -26974,30 +26964,22 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Bananas</t>
+          <t>Publix Half &amp; Half, Half Gallon</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Fresh Fruit</t>
+          <t>Cream &amp; Half-and-Half</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>46262</v>
-      </c>
-      <c r="K120" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="L120" s="2" t="n">
         <v>46268</v>
       </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
+      <c r="K120" s="1" t="n">
+        <v>5.89</v>
+      </c>
+    </row>
+    <row r="121" s="64">
       <c r="A121" s="1">
         <f>SUM(K121,M121,O121,Q121,S121,U121)</f>
         <v/>
@@ -27014,7 +26996,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Sweet Loren's Gf Brownie</t>
+          <t>Silk Soy Organic Nsa Hg</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -27029,22 +27011,28 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Sweet Loren's Gluten Free Brownie Cookie Dough</t>
+          <t>Silk Organic Unsweet Soymilk, Half Gallon</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Refrigerated Dough</t>
+          <t>Plant-Based Milk</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
         <v>46268</v>
       </c>
       <c r="K121" s="1" t="n">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="122">
+        <v>6.79</v>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="M121" s="1" t="n">
+        <v>6.79</v>
+      </c>
+    </row>
+    <row r="122" s="64">
       <c r="A122" s="1">
         <f>SUM(K122,M122,O122,Q122,S122,U122)</f>
         <v/>
@@ -27061,7 +27049,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Publix Half&amp;Half Hg</t>
+          <t>Starbucks Oat Brwn Sugar</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -27076,22 +27064,22 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Publix Half &amp; Half, Half Gallon</t>
+          <t>Starbucks Oatmilk Brown Sugar Creamer</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Cream &amp; Half-and-Half</t>
+          <t>Coffee Creamer</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
         <v>46268</v>
       </c>
       <c r="K122" s="1" t="n">
-        <v>5.89</v>
-      </c>
-    </row>
-    <row r="123">
+        <v>6.69</v>
+      </c>
+    </row>
+    <row r="123" s="64">
       <c r="A123" s="1">
         <f>SUM(K123,M123,O123,Q123,S123,U123)</f>
         <v/>
@@ -27108,7 +27096,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Silk Soy Organic Nsa Hg</t>
+          <t>Quak Rice Crisp App/Cinn</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -27123,28 +27111,22 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Silk Organic Unsweet Soymilk, Half Gallon</t>
+          <t>Quaker Rice Crisps Apple Cinnamon</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Plant-Based Milk</t>
+          <t>Rice Cakes &amp; Crisps</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
         <v>46268</v>
       </c>
       <c r="K123" s="1" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="L123" s="2" t="n">
-        <v>46268</v>
-      </c>
-      <c r="M123" s="1" t="n">
-        <v>6.79</v>
-      </c>
-    </row>
-    <row r="124">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="124" s="64">
       <c r="A124" s="1">
         <f>SUM(K124,M124,O124,Q124,S124,U124)</f>
         <v/>
@@ -27161,12 +27143,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Starbucks Oat Brwn Sugar</t>
+          <t>Quak Rice Crisp Chocolate</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -27176,22 +27158,22 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Starbucks Oatmilk Brown Sugar Creamer</t>
+          <t>Quaker Rice Crisps Chocolate</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Coffee Creamer</t>
+          <t>Rice Cakes &amp; Crisps</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
         <v>46268</v>
       </c>
       <c r="K124" s="1" t="n">
-        <v>6.69</v>
-      </c>
-    </row>
-    <row r="125">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="125" s="64">
       <c r="A125" s="1">
         <f>SUM(K125,M125,O125,Q125,S125,U125)</f>
         <v/>
@@ -27208,7 +27190,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Quak Rice Crisp App/Cinn</t>
+          <t>Klond Bar Dble Chocolate FT</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -27223,22 +27205,22 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Quaker Rice Crisps Apple Cinnamon</t>
+          <t>Klondike Double Chocolate Bar</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Rice Cakes &amp; Crisps</t>
+          <t>Frozen Desserts</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
         <v>46268</v>
       </c>
       <c r="K125" s="1" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="126">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="126" s="64">
       <c r="A126" s="1">
         <f>SUM(K126,M126,O126,Q126,S126,U126)</f>
         <v/>
@@ -27255,7 +27237,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Quak Rice Crisp Chocolate</t>
+          <t>Yasso Grk Yog Bar Coff Co FT</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -27270,22 +27252,22 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Quaker Rice Crisps Chocolate</t>
+          <t>Yasso Greek Yogurt Bars, Coffee Chocolate Chip</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Rice Cakes &amp; Crisps</t>
+          <t>Frozen Desserts</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
         <v>46268</v>
       </c>
       <c r="K126" s="1" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="127">
+        <v>6.91</v>
+      </c>
+    </row>
+    <row r="127" s="64">
       <c r="A127" s="1">
         <f>SUM(K127,M127,O127,Q127,S127,U127)</f>
         <v/>
@@ -27302,7 +27284,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Klond Bar Dble Chocolate FT</t>
+          <t>Yasso Grk Yog Bar Mntchep FT</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -27317,7 +27299,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Klondike Double Chocolate Bar</t>
+          <t>Yasso Greek Yogurt Bars, Mint Chocolate Chip</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -27329,10 +27311,10 @@
         <v>46268</v>
       </c>
       <c r="K127" s="1" t="n">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="128">
+        <v>6.91</v>
+      </c>
+    </row>
+    <row r="128" s="64">
       <c r="A128" s="1">
         <f>SUM(K128,M128,O128,Q128,S128,U128)</f>
         <v/>
@@ -27349,12 +27331,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Yasso Grk Yog Bar Coff Co FT</t>
+          <t>Dkb Org Oats &amp; Blues Brd</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -27364,22 +27346,22 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Yasso Greek Yogurt Bars, Coffee Chocolate Chip</t>
+          <t>Dave's Killer Bread Organic Oats &amp; Blues</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Frozen Desserts</t>
+          <t>Bread</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
         <v>46268</v>
       </c>
       <c r="K128" s="1" t="n">
-        <v>6.91</v>
-      </c>
-    </row>
-    <row r="129">
+        <v>6.79</v>
+      </c>
+    </row>
+    <row r="129" s="64">
       <c r="A129" s="1">
         <f>SUM(K129,M129,O129,Q129,S129,U129)</f>
         <v/>
@@ -27396,7 +27378,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Yasso Grk Yog Bar Mntchep FT</t>
+          <t>Pbx True Bleu Salad Kt</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -27411,22 +27393,22 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Yasso Greek Yogurt Bars, Mint Chocolate Chip</t>
+          <t>Publix True Bleu Salad Kit</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Frozen Desserts</t>
+          <t>Salad Kits</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
         <v>46268</v>
       </c>
-      <c r="K129" s="1" t="n">
-        <v>6.91</v>
-      </c>
-    </row>
-    <row r="130">
+      <c r="K129" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="130" s="64">
       <c r="A130" s="1">
         <f>SUM(K130,M130,O130,Q130,S130,U130)</f>
         <v/>
@@ -27443,7 +27425,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Dkb Org Oats &amp; Blues Brd</t>
+          <t>Pbx Makoto Ginger Sld</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -27458,22 +27440,22 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Dave's Killer Bread Organic Oats &amp; Blues</t>
+          <t>Publix Makoto Ginger Salad</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Bread</t>
+          <t>Salad Kits</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
         <v>46268</v>
       </c>
-      <c r="K130" s="1" t="n">
-        <v>6.79</v>
-      </c>
-    </row>
-    <row r="131">
+      <c r="K130" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="131" s="64">
       <c r="A131" s="1">
         <f>SUM(K131,M131,O131,Q131,S131,U131)</f>
         <v/>
@@ -27490,7 +27472,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Pbx True Bleu Salad Kt</t>
+          <t>Beans Green Fresh Trimmed</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -27505,22 +27487,28 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Publix True Bleu Salad Kit</t>
+          <t>Fresh Trimmed Green Beans</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Salad Kits</t>
+          <t>Fresh Vegetables</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
         <v>46268</v>
       </c>
-      <c r="K131" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="132">
+      <c r="K131" s="1" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="M131" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" s="64">
       <c r="A132" s="1">
         <f>SUM(K132,M132,O132,Q132,S132,U132)</f>
         <v/>
@@ -27537,7 +27525,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Pbx Makoto Ginger Sld</t>
+          <t>Watermelan Seedless Wedge</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -27552,22 +27540,22 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Publix Makoto Ginger Salad</t>
+          <t>Seedless Watermelon Wedge</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Salad Kits</t>
+          <t>Fresh-Cut Fruit</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
         <v>46268</v>
       </c>
-      <c r="K132" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="133">
+      <c r="K132" s="1" t="n">
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="133" s="64">
       <c r="A133" s="1">
         <f>SUM(K133,M133,O133,Q133,S133,U133)</f>
         <v/>
@@ -27584,12 +27572,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Beans Green Fresh Trimmed</t>
+          <t>limes Persian</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -27599,28 +27587,22 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Fresh Trimmed Green Beans</t>
+          <t>Persian Limes</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Fresh Vegetables</t>
+          <t>Fresh Fruit</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
         <v>46268</v>
       </c>
-      <c r="K133" s="1" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L133" s="2" t="n">
-        <v>46268</v>
-      </c>
-      <c r="M133" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134">
+      <c r="K133" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="134" s="64">
       <c r="A134" s="1">
         <f>SUM(K134,M134,O134,Q134,S134,U134)</f>
         <v/>
@@ -27637,7 +27619,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Watermelan Seedless Wedge</t>
+          <t>Salmon Fillet</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -27652,22 +27634,22 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Seedless Watermelon Wedge</t>
+          <t>Salmon Fillet</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Fresh-Cut Fruit</t>
+          <t>Fresh Seafood</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
         <v>46268</v>
       </c>
       <c r="K134" s="1" t="n">
-        <v>3.32</v>
-      </c>
-    </row>
-    <row r="135">
+        <v>46.91</v>
+      </c>
+    </row>
+    <row r="135" s="64">
       <c r="A135" s="1">
         <f>SUM(K135,M135,O135,Q135,S135,U135)</f>
         <v/>
@@ -27684,12 +27666,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>limes Persian</t>
+          <t>Dt Sp Smk Salmon PeppaG</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -27699,22 +27681,22 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Persian Limes</t>
+          <t>Smoked Salmon with Pepper</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Fresh Fruit</t>
+          <t>Smoked Seafood</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
         <v>46268</v>
       </c>
-      <c r="K135" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="136">
+      <c r="K135" s="1" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="136" s="64">
       <c r="A136" s="1">
         <f>SUM(K136,M136,O136,Q136,S136,U136)</f>
         <v/>
@@ -27731,12 +27713,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Salmon Fillet</t>
+          <t>L/Deb Cosmic Browniés</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -27746,22 +27728,22 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Salmon Fillet</t>
+          <t>Little Debbie Cosmic Brownies</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Fresh Seafood</t>
+          <t>Snack Cakes</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
         <v>46268</v>
       </c>
       <c r="K136" s="1" t="n">
-        <v>46.91</v>
-      </c>
-    </row>
-    <row r="137">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="137" s="64">
       <c r="A137" s="1">
         <f>SUM(K137,M137,O137,Q137,S137,U137)</f>
         <v/>
@@ -27778,12 +27760,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Dt Sp Smk Salmon PeppaG</t>
+          <t>Magen David Blackberry</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>T</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -27793,22 +27775,22 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Smoked Salmon with Pepper</t>
+          <t>Magen David Blackberry Wine</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Smoked Seafood</t>
+          <t>Wine</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
         <v>46268</v>
       </c>
       <c r="K137" s="1" t="n">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="138">
+        <v>7.19</v>
+      </c>
+    </row>
+    <row r="138" s="64">
       <c r="A138" s="1">
         <f>SUM(K138,M138,O138,Q138,S138,U138)</f>
         <v/>
@@ -27825,12 +27807,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>L/Deb Cosmic Browniés</t>
+          <t>Ka Flour Bread Unbl 10Lb</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -27840,22 +27822,22 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Little Debbie Cosmic Brownies</t>
+          <t>King Arthur Unbleached Bread Flour, 10 lb</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Snack Cakes</t>
+          <t>Baking Ingredients</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
         <v>46268</v>
       </c>
       <c r="K138" s="1" t="n">
-        <v>3.19</v>
-      </c>
-    </row>
-    <row r="139">
+        <v>11.59</v>
+      </c>
+    </row>
+    <row r="139" s="64">
       <c r="A139" s="1">
         <f>SUM(K139,M139,O139,Q139,S139,U139)</f>
         <v/>
@@ -27872,12 +27854,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Magen David Blackberry</t>
+          <t>Mango</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -27887,22 +27869,22 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Magen David Blackberry Wine</t>
+          <t>Mango</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Wine</t>
+          <t>Fresh Fruit</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
         <v>46268</v>
       </c>
       <c r="K139" s="1" t="n">
-        <v>7.19</v>
-      </c>
-    </row>
-    <row r="140">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="140" s="64">
       <c r="A140" s="1">
         <f>SUM(K140,M140,O140,Q140,S140,U140)</f>
         <v/>
@@ -27919,12 +27901,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Ka Flour Bread Unbl 10Lb</t>
+          <t>Sales Tax 7%</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>T</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -27934,22 +27916,22 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>King Arthur Unbleached Bread Flour, 10 lb</t>
+          <t>Sales Tax</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Baking Ingredients</t>
+          <t>Fees &amp; Charges</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
         <v>46268</v>
       </c>
       <c r="K140" s="1" t="n">
-        <v>11.59</v>
-      </c>
-    </row>
-    <row r="141">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="141" s="64">
       <c r="A141" s="1">
         <f>SUM(K141,M141,O141,Q141,S141,U141)</f>
         <v/>
@@ -27966,7 +27948,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Mango</t>
+          <t>Bananas</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -27981,7 +27963,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Mango</t>
+          <t>Bananas</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -27993,104 +27975,104 @@
         <v>46268</v>
       </c>
       <c r="K141" s="1" t="n">
-        <v>2.99</v>
-      </c>
-    </row>
-    <row r="142">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="142" s="64">
       <c r="A142" s="1">
         <f>SUM(K142,M142,O142,Q142,S142,U142)</f>
         <v/>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>Aldi</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
+          <t>701574</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Frmhse Rnch Chd</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Sales Tax 7%</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Sales Tax</t>
+          <t>Farmhouse Ranch Cheddar</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Fees &amp; Charges</t>
+          <t>Cheese</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>46268</v>
-      </c>
-      <c r="K142" s="1" t="n">
-        <v>1.87</v>
-      </c>
-    </row>
-    <row r="143">
+        <v>46271</v>
+      </c>
+      <c r="K142" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="143" s="64">
       <c r="A143" s="1">
         <f>SUM(K143,M143,O143,Q143,S143,U143)</f>
         <v/>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>Aldi</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
+          <t>356457</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Organic Kale</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Bananas</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Bananas</t>
+          <t>Organic Kale</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Fresh Fruit</t>
+          <t>Fresh Vegetables</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>46268</v>
-      </c>
-      <c r="K143" s="1" t="n">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="144">
+        <v>46271</v>
+      </c>
+      <c r="K143" t="n">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="144" s="64">
       <c r="A144" s="1">
         <f>SUM(K144,M144,O144,Q144,S144,U144)</f>
         <v/>
@@ -28102,12 +28084,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>701574</t>
+          <t>356591</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Frmhse Rnch Chd</t>
+          <t>Pink Lady Apple</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -28122,22 +28104,22 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Farmhouse Ranch Cheddar</t>
+          <t>Pink Lady Apples</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Cheese</t>
+          <t>Fresh Fruit</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
         <v>46271</v>
       </c>
       <c r="K144" t="n">
-        <v>3.29</v>
-      </c>
-    </row>
-    <row r="145">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="145" s="64">
       <c r="A145" s="1">
         <f>SUM(K145,M145,O145,Q145,S145,U145)</f>
         <v/>
@@ -28149,12 +28131,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>356457</t>
+          <t>356686</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Organic Kale</t>
+          <t>Little Yellows</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -28169,7 +28151,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Organic Kale</t>
+          <t>Little Yellow Potatoes</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -28181,10 +28163,10 @@
         <v>46271</v>
       </c>
       <c r="K145" t="n">
-        <v>3.19</v>
-      </c>
-    </row>
-    <row r="146">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="146" s="64">
       <c r="A146" s="1">
         <f>SUM(K146,M146,O146,Q146,S146,U146)</f>
         <v/>
@@ -28196,12 +28178,12 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>356591</t>
+          <t>356427</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Pink Lady Apple</t>
+          <t>Multi-Peppers 3</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -28216,22 +28198,22 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Pink Lady Apples</t>
+          <t>Multi-Color Peppers, 3-Pack</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Fresh Fruit</t>
+          <t>Fresh Vegetables</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
         <v>46271</v>
       </c>
       <c r="K146" t="n">
-        <v>3.69</v>
-      </c>
-    </row>
-    <row r="147">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="147" s="64">
       <c r="A147" s="1">
         <f>SUM(K147,M147,O147,Q147,S147,U147)</f>
         <v/>
@@ -28243,12 +28225,12 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>356686</t>
+          <t>396384</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Little Yellows</t>
+          <t>Green Grapes LRW</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -28263,22 +28245,22 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Little Yellow Potatoes</t>
+          <t>Green Grapes</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Fresh Vegetables</t>
+          <t>Fresh Fruit</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
         <v>46271</v>
       </c>
       <c r="K147" t="n">
-        <v>3.29</v>
-      </c>
-    </row>
-    <row r="148">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="148" s="64">
       <c r="A148" s="1">
         <f>SUM(K148,M148,O148,Q148,S148,U148)</f>
         <v/>
@@ -28290,12 +28272,12 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>356427</t>
+          <t>356417</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Multi-Peppers 3</t>
+          <t>Mandarins</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -28310,22 +28292,22 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Multi-Color Peppers, 3-Pack</t>
+          <t>Mandarins</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Fresh Vegetables</t>
+          <t>Fresh Fruit</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
         <v>46271</v>
       </c>
       <c r="K148" t="n">
-        <v>2.69</v>
-      </c>
-    </row>
-    <row r="149">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="149" s="64">
       <c r="A149" s="1">
         <f>SUM(K149,M149,O149,Q149,S149,U149)</f>
         <v/>
@@ -28337,12 +28319,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>396384</t>
+          <t>692109</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Green Grapes LRW</t>
+          <t>Org Celery Heart</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -28357,22 +28339,22 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Green Grapes</t>
+          <t>Organic Celery Hearts</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Fresh Fruit</t>
+          <t>Fresh Vegetables</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
         <v>46271</v>
       </c>
       <c r="K149" t="n">
-        <v>3.81</v>
-      </c>
-    </row>
-    <row r="150">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="150" s="64">
       <c r="A150" s="1">
         <f>SUM(K150,M150,O150,Q150,S150,U150)</f>
         <v/>
@@ -28384,12 +28366,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>356417</t>
+          <t>466249</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Mandarins</t>
+          <t>Head &amp; Shoulders</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -28404,22 +28386,22 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Mandarins</t>
+          <t>Head &amp; Shoulders</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Fresh Fruit</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
         <v>46271</v>
       </c>
       <c r="K150" t="n">
-        <v>2.89</v>
-      </c>
-    </row>
-    <row r="151">
+        <v>6.97</v>
+      </c>
+    </row>
+    <row r="151" s="64">
       <c r="A151" s="1">
         <f>SUM(K151,M151,O151,Q151,S151,U151)</f>
         <v/>
@@ -28431,12 +28413,12 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>692109</t>
+          <t>399518</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Org Celery Heart</t>
+          <t>Salt Grinders</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -28451,22 +28433,22 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Organic Celery Hearts</t>
+          <t>Salt Grinder</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Fresh Vegetables</t>
+          <t>Seasonings &amp; Spices</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
         <v>46271</v>
       </c>
       <c r="K151" t="n">
-        <v>2.59</v>
-      </c>
-    </row>
-    <row r="152">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="152" s="64">
       <c r="A152" s="1">
         <f>SUM(K152,M152,O152,Q152,S152,U152)</f>
         <v/>
@@ -28478,12 +28460,12 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>466249</t>
+          <t>399025</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Head &amp; Shoulders</t>
+          <t>Peppercorn Grinder</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -28498,22 +28480,22 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Head &amp; Shoulders</t>
+          <t>Peppercorn Grinder</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Seasonings &amp; Spices</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
         <v>46271</v>
       </c>
       <c r="K152" t="n">
-        <v>6.97</v>
-      </c>
-    </row>
-    <row r="153">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="153" s="64">
       <c r="A153" s="1">
         <f>SUM(K153,M153,O153,Q153,S153,U153)</f>
         <v/>
@@ -28525,12 +28507,12 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>399518</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Salt Grinders</t>
+          <t>Brocoli Crowns</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -28545,22 +28527,22 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Salt Grinder</t>
+          <t>Broccoli Crowns</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Seasonings &amp; Spices</t>
+          <t>Fresh Vegetables</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
         <v>46271</v>
       </c>
       <c r="K153" t="n">
-        <v>1.59</v>
-      </c>
-    </row>
-    <row r="154">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="154" s="64">
       <c r="A154" s="1">
         <f>SUM(K154,M154,O154,Q154,S154,U154)</f>
         <v/>
@@ -28572,12 +28554,12 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>399025</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Peppercorn Grinder</t>
+          <t>Banannas LRW</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -28592,22 +28574,22 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Peppercorn Grinder</t>
+          <t>Bananas</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Seasonings &amp; Spices</t>
+          <t>Fresh Fruit</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
         <v>46271</v>
       </c>
       <c r="K154" t="n">
-        <v>2.29</v>
-      </c>
-    </row>
-    <row r="155">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="155" s="64">
       <c r="A155" s="1">
         <f>SUM(K155,M155,O155,Q155,S155,U155)</f>
         <v/>
@@ -28624,7 +28606,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Brocoli Crowns</t>
+          <t>Blueberries</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -28639,22 +28621,22 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Broccoli Crowns</t>
+          <t>Blueberries</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Fresh Vegetables</t>
+          <t>Fresh Fruit</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
         <v>46271</v>
       </c>
       <c r="K155" t="n">
-        <v>3.95</v>
-      </c>
-    </row>
-    <row r="156">
+        <v>5.98</v>
+      </c>
+    </row>
+    <row r="156" s="64">
       <c r="A156" s="1">
         <f>SUM(K156,M156,O156,Q156,S156,U156)</f>
         <v/>
@@ -28671,7 +28653,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Banannas LRW</t>
+          <t>Raspberries</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -28686,7 +28668,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Bananas</t>
+          <t>Raspberries</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -28698,10 +28680,10 @@
         <v>46271</v>
       </c>
       <c r="K156" t="n">
-        <v>1.66</v>
-      </c>
-    </row>
-    <row r="157">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="157" s="64">
       <c r="A157" s="1">
         <f>SUM(K157,M157,O157,Q157,S157,U157)</f>
         <v/>
@@ -28718,7 +28700,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Blueberries</t>
+          <t>Strawberries</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -28733,7 +28715,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Blueberries</t>
+          <t>Strawberries</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -28745,10 +28727,10 @@
         <v>46271</v>
       </c>
       <c r="K157" t="n">
-        <v>5.98</v>
-      </c>
-    </row>
-    <row r="158">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="158" s="64">
       <c r="A158" s="1">
         <f>SUM(K158,M158,O158,Q158,S158,U158)</f>
         <v/>
@@ -28765,7 +28747,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Raspberries</t>
+          <t>GF Wide Pan Bread</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -28780,22 +28762,22 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Raspberries</t>
+          <t>Gluten-Free Wide Pan Bread</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Fresh Fruit</t>
+          <t>Bread</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
         <v>46271</v>
       </c>
       <c r="K158" t="n">
-        <v>2.69</v>
-      </c>
-    </row>
-    <row r="159">
+        <v>6.79</v>
+      </c>
+    </row>
+    <row r="159" s="64">
       <c r="A159" s="1">
         <f>SUM(K159,M159,O159,Q159,S159,U159)</f>
         <v/>
@@ -28812,7 +28794,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Strawberries</t>
+          <t>Artisinal Buns</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -28827,22 +28809,22 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Strawberries</t>
+          <t>Artisanal Buns</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Fresh Fruit</t>
+          <t>Bread</t>
         </is>
       </c>
       <c r="J159" s="2" t="n">
         <v>46271</v>
       </c>
       <c r="K159" t="n">
-        <v>2.29</v>
-      </c>
-    </row>
-    <row r="160">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="160" s="64">
       <c r="A160" s="1">
         <f>SUM(K160,M160,O160,Q160,S160,U160)</f>
         <v/>
@@ -28859,7 +28841,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>GF Wide Pan Bread</t>
+          <t>Organic Chickpeas</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -28874,22 +28856,22 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Gluten-Free Wide Pan Bread</t>
+          <t>Organic Chickpeas</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Bread</t>
+          <t>Canned Beans &amp; Legumes</t>
         </is>
       </c>
       <c r="J160" s="2" t="n">
         <v>46271</v>
       </c>
       <c r="K160" t="n">
-        <v>6.79</v>
-      </c>
-    </row>
-    <row r="161">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="161" s="64">
       <c r="A161" s="1">
         <f>SUM(K161,M161,O161,Q161,S161,U161)</f>
         <v/>
@@ -28906,7 +28888,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Artisinal Buns</t>
+          <t>Pil Flaky Biscuits</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -28921,22 +28903,22 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Artisanal Buns</t>
+          <t>Pillsbury Flaky Biscuits</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Bread</t>
+          <t>Refrigerated Dough</t>
         </is>
       </c>
       <c r="J161" s="2" t="n">
         <v>46271</v>
       </c>
       <c r="K161" t="n">
-        <v>2.99</v>
-      </c>
-    </row>
-    <row r="162">
+        <v>2.97</v>
+      </c>
+    </row>
+    <row r="162" s="64">
       <c r="A162" s="1">
         <f>SUM(K162,M162,O162,Q162,S162,U162)</f>
         <v/>
@@ -28948,19 +28930,19 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
+          <t>383249</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Deli Sliced CoJack</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Organic Chickpeas</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="G162" t="inlineStr">
         <is>
           <t>238</t>
@@ -28968,22 +28950,22 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Organic Chickpeas</t>
+          <t>Deli-Sliced Colby Jack Cheese</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Canned Beans &amp; Legumes</t>
+          <t>Cheese</t>
         </is>
       </c>
       <c r="J162" s="2" t="n">
         <v>46271</v>
       </c>
-      <c r="K162" t="n">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="163">
+      <c r="K162" s="1" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="163" s="64">
       <c r="A163" s="1">
         <f>SUM(K163,M163,O163,Q163,S163,U163)</f>
         <v/>
@@ -28995,19 +28977,19 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
+          <t>383252</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Deli Sliced Cheese</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Pil Flaky Biscuits</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="G163" t="inlineStr">
         <is>
           <t>238</t>
@@ -29015,22 +28997,22 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Pillsbury Flaky Biscuits</t>
+          <t>Deli-Sliced Cheese</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Refrigerated Dough</t>
+          <t>Cheese</t>
         </is>
       </c>
       <c r="J163" s="2" t="n">
         <v>46271</v>
       </c>
-      <c r="K163" t="n">
-        <v>2.97</v>
-      </c>
-    </row>
-    <row r="164">
+      <c r="K163" s="1" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="164" s="64">
       <c r="A164" s="1">
         <f>SUM(K164,M164,O164,Q164,S164,U164)</f>
         <v/>
@@ -29042,12 +29024,12 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>383249</t>
+          <t>382473</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Deli Sliced CoJack</t>
+          <t>Shredded Mozz</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -29062,7 +29044,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Deli-Sliced Colby Jack Cheese</t>
+          <t>Shredded Mozzarella Cheese</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -29074,10 +29056,10 @@
         <v>46271</v>
       </c>
       <c r="K164" s="1" t="n">
-        <v>1.49</v>
-      </c>
-    </row>
-    <row r="165">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="165" s="64">
       <c r="A165" s="1">
         <f>SUM(K165,M165,O165,Q165,S165,U165)</f>
         <v/>
@@ -29089,12 +29071,12 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>383252</t>
+          <t>380809</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Deli Sliced Cheese</t>
+          <t>2 Roll Paper Towel</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -29109,22 +29091,22 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Deli-Sliced Cheese</t>
+          <t>Paper Towels, 2-Roll</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Cheese</t>
+          <t>Paper Towels</t>
         </is>
       </c>
       <c r="J165" s="2" t="n">
         <v>46271</v>
       </c>
       <c r="K165" s="1" t="n">
-        <v>1.49</v>
-      </c>
-    </row>
-    <row r="166">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="166" s="64">
       <c r="A166" s="1">
         <f>SUM(K166,M166,O166,Q166,S166,U166)</f>
         <v/>
@@ -29136,12 +29118,12 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>382473</t>
+          <t>344280</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Shredded Mozz</t>
+          <t>Cauli Crust Pizza</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -29156,22 +29138,22 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Shredded Mozzarella Cheese</t>
+          <t>Cauliflower Crust Pizza</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Cheese</t>
+          <t>Frozen Pizza</t>
         </is>
       </c>
       <c r="J166" s="2" t="n">
         <v>46271</v>
       </c>
       <c r="K166" s="1" t="n">
-        <v>3.29</v>
-      </c>
-    </row>
-    <row r="167">
+        <v>8.289999999999999</v>
+      </c>
+    </row>
+    <row r="167" s="64">
       <c r="A167" s="1">
         <f>SUM(K167,M167,O167,Q167,S167,U167)</f>
         <v/>
@@ -29183,12 +29165,12 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>380809</t>
+          <t>272135</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2 Roll Paper Towel</t>
+          <t>Salmon Portions</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -29203,22 +29185,22 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Paper Towels, 2-Roll</t>
+          <t>Salmon Portions</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Paper Towels</t>
+          <t>Fresh Seafood</t>
         </is>
       </c>
       <c r="J167" s="2" t="n">
         <v>46271</v>
       </c>
       <c r="K167" s="1" t="n">
-        <v>3.89</v>
-      </c>
-    </row>
-    <row r="168">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="168" s="64">
       <c r="A168" s="1">
         <f>SUM(K168,M168,O168,Q168,S168,U168)</f>
         <v/>
@@ -29230,12 +29212,12 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>344280</t>
+          <t>388137</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Cauli Crust Pizza</t>
+          <t>Large Eggs</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -29250,22 +29232,22 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Cauliflower Crust Pizza</t>
+          <t>Large Eggs</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Frozen Pizza</t>
+          <t>Eggs</t>
         </is>
       </c>
       <c r="J168" s="2" t="n">
         <v>46271</v>
       </c>
-      <c r="K168" s="1" t="n">
-        <v>8.289999999999999</v>
-      </c>
-    </row>
-    <row r="169">
+      <c r="K168" t="n">
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="169" s="64">
       <c r="A169" s="1">
         <f>SUM(K169,M169,O169,Q169,S169,U169)</f>
         <v/>
@@ -29277,12 +29259,12 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>272135</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Salmon Portions</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -29297,39 +29279,39 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Salmon Portions</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Fresh Seafood</t>
+          <t>Fees &amp; Charges</t>
         </is>
       </c>
       <c r="J169" s="2" t="n">
         <v>46271</v>
       </c>
-      <c r="K169" s="1" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="170">
+      <c r="K169" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="170" s="64">
       <c r="A170" s="1">
         <f>SUM(K170,M170,O170,Q170,S170,U170)</f>
         <v/>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Aldi</t>
+          <t>Trader Joe's</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>388137</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Large Eggs</t>
+          <t>EMPIRE KOSHER GROUND TRK</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -29339,34 +29321,64 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>0848</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Large Eggs</t>
+          <t>Empire Kosher Ground Turkey</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Eggs</t>
+          <t>Fresh Poultry</t>
         </is>
       </c>
       <c r="J170" s="2" t="n">
-        <v>46271</v>
-      </c>
-      <c r="K170" t="n">
-        <v>3.32</v>
-      </c>
-    </row>
-    <row r="171">
+        <v>46258</v>
+      </c>
+      <c r="K170" s="1" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>46258</v>
+      </c>
+      <c r="M170" s="1" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="N170" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O170" s="1" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="P170" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="R170" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="S170" s="1" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="T170" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="U170" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="171" s="64">
       <c r="A171" s="1">
         <f>SUM(K171,M171,O171,Q171,S171,U171)</f>
         <v/>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Aldi</t>
+          <t>Trader Joe's</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -29376,7 +29388,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>MUFFIN BLUEBERRY GLUTEN</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -29386,27 +29398,43 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>0848</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Gluten-Free Blueberry Muffins</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Fees &amp; Charges</t>
+          <t>Muffins &amp; Pastries</t>
         </is>
       </c>
       <c r="J171" s="2" t="n">
-        <v>46271</v>
-      </c>
-      <c r="K171" t="n">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="172">
+        <v>46258</v>
+      </c>
+      <c r="K171" s="1" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="L171" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" s="64">
       <c r="A172" s="1">
         <f>SUM(K172,M172,O172,Q172,S172,U172)</f>
         <v/>
@@ -29423,7 +29451,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>EMPIRE KOSHER GROUND TRK</t>
+          <t>TAQUITOS BLACK BEAN &amp; CH</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -29438,52 +29466,22 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Empire Kosher Ground Turkey</t>
+          <t>Black Bean &amp; Cheese Taquitos</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Fresh Poultry</t>
+          <t>Frozen Appetizers</t>
         </is>
       </c>
       <c r="J172" s="2" t="n">
-        <v>46258</v>
-      </c>
-      <c r="K172" s="1" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="L172" s="2" t="n">
-        <v>46258</v>
-      </c>
-      <c r="M172" s="1" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="N172" s="2" t="n">
         <v>46272</v>
       </c>
-      <c r="O172" s="1" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="P172" s="2" t="n">
-        <v>46272</v>
-      </c>
-      <c r="Q172" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="R172" s="2" t="n">
-        <v>46272</v>
-      </c>
-      <c r="S172" s="1" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="T172" s="2" t="n">
-        <v>46272</v>
-      </c>
-      <c r="U172" t="n">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="173">
+      <c r="K172" t="n">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="173" s="64">
       <c r="A173" s="1">
         <f>SUM(K173,M173,O173,Q173,S173,U173)</f>
         <v/>
@@ -29500,7 +29498,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>MUFFIN BLUEBERRY GLUTEN</t>
+          <t>EMPIRE KOSHER TRKY HALF</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -29515,38 +29513,22 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Gluten-Free Blueberry Muffins</t>
+          <t>Empire Kosher Turkey Half</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Muffins &amp; Pastries</t>
+          <t>Fresh Poultry</t>
         </is>
       </c>
       <c r="J173" s="2" t="n">
-        <v>46258</v>
-      </c>
-      <c r="K173" s="1" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="L173" s="2" t="n">
         <v>46272</v>
       </c>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N173" s="2" t="n">
-        <v>46272</v>
-      </c>
-      <c r="O173" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
+      <c r="K173" t="n">
+        <v>19.16</v>
+      </c>
+    </row>
+    <row r="174" s="64">
       <c r="A174" s="1">
         <f>SUM(K174,M174,O174,Q174,S174,U174)</f>
         <v/>
@@ -29563,7 +29545,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>TAQUITOS BLACK BEAN &amp; CH</t>
+          <t>EMPIRE KOSHER BNL/SKNL B</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -29578,22 +29560,28 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Black Bean &amp; Cheese Taquitos</t>
+          <t>Empire Kosher Boneless Skinless Chicken Breast</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Frozen Appetizers</t>
+          <t>Fresh Poultry</t>
         </is>
       </c>
       <c r="J174" s="2" t="n">
         <v>46272</v>
       </c>
-      <c r="K174" t="n">
-        <v>4.49</v>
-      </c>
-    </row>
-    <row r="175">
+      <c r="K174" s="1" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="M174" s="1" t="n">
+        <v>10.95</v>
+      </c>
+    </row>
+    <row r="175" s="64">
       <c r="A175" s="1">
         <f>SUM(K175,M175,O175,Q175,S175,U175)</f>
         <v/>
@@ -29610,12 +29598,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>EMPIRE KOSHER TRKY HALF</t>
+          <t>BEEF KOSHER GROUND 85/15</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -29625,22 +29613,22 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Empire Kosher Turkey Half</t>
+          <t>Kosher Ground Beef 85/15</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Fresh Poultry</t>
+          <t>Fresh Beef</t>
         </is>
       </c>
       <c r="J175" s="2" t="n">
         <v>46272</v>
       </c>
-      <c r="K175" t="n">
-        <v>19.16</v>
-      </c>
-    </row>
-    <row r="176">
+      <c r="K175" s="1" t="n">
+        <v>35.97</v>
+      </c>
+    </row>
+    <row r="176" s="64">
       <c r="A176" s="1">
         <f>SUM(K176,M176,O176,Q176,S176,U176)</f>
         <v/>
@@ -29657,7 +29645,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>EMPIRE KOSHER BNL/SKNL B</t>
+          <t>CHOCOLATE BABKA</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -29672,28 +29660,22 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Empire Kosher Boneless Skinless Chicken Breast</t>
+          <t>Chocolate Babka</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Fresh Poultry</t>
+          <t>Muffins &amp; Pastries</t>
         </is>
       </c>
       <c r="J176" s="2" t="n">
         <v>46272</v>
       </c>
-      <c r="K176" s="1" t="n">
-        <v>10.79</v>
-      </c>
-      <c r="L176" s="2" t="n">
-        <v>46272</v>
-      </c>
-      <c r="M176" s="1" t="n">
-        <v>10.95</v>
-      </c>
-    </row>
-    <row r="177">
+      <c r="K176" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="177" s="64">
       <c r="A177" s="1">
         <f>SUM(K177,M177,O177,Q177,S177,U177)</f>
         <v/>
@@ -29710,12 +29692,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>BEEF KOSHER GROUND 85/15</t>
+          <t>R-SALAD COMPLETE SWEET K</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -29725,22 +29707,22 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Kosher Ground Beef 85/15</t>
+          <t>Complete Sweet Kale Salad Kit</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Fresh Beef</t>
+          <t>Salad Kits</t>
         </is>
       </c>
       <c r="J177" s="2" t="n">
         <v>46272</v>
       </c>
-      <c r="K177" s="1" t="n">
-        <v>35.97</v>
-      </c>
-    </row>
-    <row r="178">
+      <c r="K177" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="178" s="64">
       <c r="A178" s="1">
         <f>SUM(K178,M178,O178,Q178,S178,U178)</f>
         <v/>
@@ -29757,7 +29739,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>CHOCOLATE BABKA</t>
+          <t>HALF MOON  COOKIES</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -29772,22 +29754,22 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Chocolate Babka</t>
+          <t>Half Moon Cookies</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Muffins &amp; Pastries</t>
+          <t>Cookies</t>
         </is>
       </c>
       <c r="J178" s="2" t="n">
         <v>46272</v>
       </c>
       <c r="K178" t="n">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="179">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="179" s="64">
       <c r="A179" s="1">
         <f>SUM(K179,M179,O179,Q179,S179,U179)</f>
         <v/>
@@ -29804,7 +29786,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>R-SALAD COMPLETE SWEET K</t>
+          <t xml:space="preserve">HOL PUMPKIN CREAM CHEESE </t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -29819,29 +29801,29 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Complete Sweet Kale Salad Kit</t>
+          <t>Pumpkin Cream Cheese</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Salad Kits</t>
+          <t>Cream Cheese</t>
         </is>
       </c>
       <c r="J179" s="2" t="n">
         <v>46272</v>
       </c>
       <c r="K179" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="180">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="180" s="64">
       <c r="A180" s="1">
         <f>SUM(K180,M180,O180,Q180,S180,U180)</f>
         <v/>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Trader Joe's</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -29851,7 +29833,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>HALF MOON  COOKIES</t>
+          <t>Chobani Fob 0% Blk Chry</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -29861,34 +29843,40 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>0848</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Half Moon Cookies</t>
+          <t>Chobani Black Cherry Greek Yogurt</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Cookies</t>
+          <t>Yogurt</t>
         </is>
       </c>
       <c r="J180" s="2" t="n">
         <v>46272</v>
       </c>
       <c r="K180" t="n">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="181">
+        <v>1</v>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="M180" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" s="64">
       <c r="A181" s="1">
         <f>SUM(K181,M181,O181,Q181,S181,U181)</f>
         <v/>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Trader Joe's</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -29898,7 +29886,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">HOL PUMPKIN CREAM CHEESE </t>
+          <t>Mc Cinn Grnd 2.370oz</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -29908,27 +29896,27 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>0848</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Pumpkin Cream Cheese</t>
+          <t>McCormick Ground Cinnamon</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Cream Cheese</t>
+          <t>Seasonings &amp; Spices</t>
         </is>
       </c>
       <c r="J181" s="2" t="n">
         <v>46272</v>
       </c>
       <c r="K181" t="n">
-        <v>2.79</v>
-      </c>
-    </row>
-    <row r="182">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="182" s="64">
       <c r="A182" s="1">
         <f>SUM(K182,M182,O182,Q182,S182,U182)</f>
         <v/>
@@ -29945,7 +29933,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Chobani Fob 0% Blk Chry</t>
+          <t>Chobani Fob 2% Pineappple</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -29960,7 +29948,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Chobani Black Cherry Greek Yogurt</t>
+          <t>Chobani Pineapple Greek Yogurt</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -29974,14 +29962,8 @@
       <c r="K182" t="n">
         <v>1</v>
       </c>
-      <c r="L182" s="2" t="n">
-        <v>46272</v>
-      </c>
-      <c r="M182" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="183">
+    </row>
+    <row r="183" s="64">
       <c r="A183" s="1">
         <f>SUM(K183,M183,O183,Q183,S183,U183)</f>
         <v/>
@@ -29998,7 +29980,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Mc Cinn Grnd 2.370oz</t>
+          <t>Chobani Hero Batch Fob</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -30013,22 +29995,22 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>McCormick Ground Cinnamon</t>
+          <t>Chobani Hero Batch Greek Yogurt</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Seasonings &amp; Spices</t>
+          <t>Yogurt</t>
         </is>
       </c>
       <c r="J183" s="2" t="n">
         <v>46272</v>
       </c>
       <c r="K183" t="n">
-        <v>3.29</v>
-      </c>
-    </row>
-    <row r="184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" s="64">
       <c r="A184" s="1">
         <f>SUM(K184,M184,O184,Q184,S184,U184)</f>
         <v/>
@@ -30045,7 +30027,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Chobani Fob 2% Pineappple</t>
+          <t>Chobani Blnd  2% Key Lime</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -30060,7 +30042,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Chobani Pineapple Greek Yogurt</t>
+          <t>Chobani Key Lime Greek Yogurt</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -30075,7 +30057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" s="64">
       <c r="A185" s="1">
         <f>SUM(K185,M185,O185,Q185,S185,U185)</f>
         <v/>
@@ -30122,7 +30104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" s="64">
       <c r="A186" s="1">
         <f>SUM(K186,M186,O186,Q186,S186,U186)</f>
         <v/>
@@ -30139,7 +30121,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Chobani Blnd  2% Key Lime</t>
+          <t>Chobani Fob 2% Stwbry Ban</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -30154,7 +30136,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Chobani Key Lime Greek Yogurt</t>
+          <t>Chobani Strawberry Banana Greek Yogurt</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -30169,7 +30151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" s="64">
       <c r="A187" s="1">
         <f>SUM(K187,M187,O187,Q187,S187,U187)</f>
         <v/>
@@ -30186,7 +30168,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Chobani Hero Batch Fob</t>
+          <t>Chobani Fob 0% Blk Chry</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -30201,7 +30183,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Chobani Hero Batch Greek Yogurt</t>
+          <t>Chobani Black Cherry Greek Yogurt</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -30216,7 +30198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" s="64">
       <c r="A188" s="1">
         <f>SUM(K188,M188,O188,Q188,S188,U188)</f>
         <v/>
@@ -30233,7 +30215,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Chobani Fob 2% Stwbry Ban</t>
+          <t>Chobani 20G Drk 4pk Straw</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -30248,7 +30230,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Chobani Strawberry Banana Greek Yogurt</t>
+          <t>Chobani Protein Greek Yogurt Drink, Strawberries &amp; Cream</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -30260,10 +30242,10 @@
         <v>46272</v>
       </c>
       <c r="K188" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="189">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="189" s="64">
       <c r="A189" s="1">
         <f>SUM(K189,M189,O189,Q189,S189,U189)</f>
         <v/>
@@ -30280,7 +30262,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Chobani Fob 0% Blk Chry</t>
+          <t xml:space="preserve">Sm Raisins Golden </t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -30295,22 +30277,22 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Chobani Black Cherry Greek Yogurt</t>
+          <t>Sun-Maid Golden Raisins</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Yogurt</t>
+          <t>Dried Fruit</t>
         </is>
       </c>
       <c r="J189" s="2" t="n">
         <v>46272</v>
       </c>
       <c r="K189" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="190">
+        <v>4.45</v>
+      </c>
+    </row>
+    <row r="190" s="64">
       <c r="A190" s="1">
         <f>SUM(K190,M190,O190,Q190,S190,U190)</f>
         <v/>
@@ -30327,7 +30309,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Chobani 20G Drk 4pk Straw</t>
+          <t>Cho 4pk Flip Lto</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -30342,7 +30324,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Chobani Protein Greek Yogurt Drink, Strawberries &amp; Cream</t>
+          <t>Chobani Flip 4-Pack</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -30354,17 +30336,17 @@
         <v>46272</v>
       </c>
       <c r="K190" t="n">
-        <v>10.99</v>
-      </c>
-    </row>
-    <row r="191">
+        <v>7.19</v>
+      </c>
+    </row>
+    <row r="191" s="64">
       <c r="A191" s="1">
         <f>SUM(K191,M191,O191,Q191,S191,U191)</f>
         <v/>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>PapaJohns</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -30374,7 +30356,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sm Raisins Golden </t>
+          <t>Large NY Style 1-Topping Pizza</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -30382,36 +30364,34 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
+      <c r="G191" t="n">
+        <v>0</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Sun-Maid Golden Raisins</t>
+          <t>Papa John's Large NY Style 1-Topping Pizza</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Dried Fruit</t>
+          <t>Prepared Meals</t>
         </is>
       </c>
       <c r="J191" s="2" t="n">
         <v>46272</v>
       </c>
       <c r="K191" t="n">
-        <v>4.45</v>
-      </c>
-    </row>
-    <row r="192">
+        <v>17.33</v>
+      </c>
+    </row>
+    <row r="192" s="64">
       <c r="A192" s="1">
         <f>SUM(K192,M192,O192,Q192,S192,U192)</f>
         <v/>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>PapaJohns</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -30421,7 +30401,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Cho 4pk Flip Lto</t>
+          <t>Pizza + Wings + Cheesesticks</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -30429,36 +30409,34 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
+      <c r="G192" t="n">
+        <v>0</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Chobani Flip 4-Pack</t>
+          <t>Papa John's Pizza, Wings &amp; Cheesesticks</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Yogurt</t>
+          <t>Prepared Meals</t>
         </is>
       </c>
       <c r="J192" s="2" t="n">
         <v>46272</v>
       </c>
       <c r="K192" t="n">
-        <v>7.19</v>
-      </c>
-    </row>
-    <row r="193">
+        <v>39.37</v>
+      </c>
+    </row>
+    <row r="193" s="64">
       <c r="A193" s="1">
         <f>SUM(K193,M193,O193,Q193,S193,U193)</f>
         <v/>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>PapaJohns</t>
+          <t>SurfinTurtle</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -30468,7 +30446,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Large NY Style 1-Topping Pizza</t>
+          <t>Pineapple Dole Whip Cup</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -30476,12 +30454,14 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="G193" t="n">
-        <v>0</v>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Papa John's Large NY Style 1-Topping Pizza</t>
+          <t>Pineapple Dole Whip Cup</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -30490,20 +30470,20 @@
         </is>
       </c>
       <c r="J193" s="2" t="n">
-        <v>46272</v>
-      </c>
-      <c r="K193" t="n">
-        <v>17.33</v>
-      </c>
-    </row>
-    <row r="194">
+        <v>46274</v>
+      </c>
+      <c r="K193" s="1" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="194" s="64">
       <c r="A194" s="1">
         <f>SUM(K194,M194,O194,Q194,S194,U194)</f>
         <v/>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>PapaJohns</t>
+          <t>SurfinTurtle</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -30513,7 +30493,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Pizza + Wings + Cheesesticks</t>
+          <t>Hot Fudge ($</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -30521,12 +30501,14 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="G194" t="n">
-        <v>0</v>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Papa John's Pizza, Wings &amp; Cheesesticks</t>
+          <t>Hot Fudge</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -30535,13 +30517,13 @@
         </is>
       </c>
       <c r="J194" s="2" t="n">
-        <v>46272</v>
-      </c>
-      <c r="K194" t="n">
-        <v>39.37</v>
-      </c>
-    </row>
-    <row r="195">
+        <v>46274</v>
+      </c>
+      <c r="K194" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" s="64">
       <c r="A195" s="1">
         <f>SUM(K195,M195,O195,Q195,S195,U195)</f>
         <v/>
@@ -30558,7 +30540,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Pineapple Dole Whip Cup</t>
+          <t>Arctic Cyclone</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -30573,7 +30555,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Pineapple Dole Whip Cup</t>
+          <t>Arctic Cyclone</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -30585,10 +30567,10 @@
         <v>46274</v>
       </c>
       <c r="K195" s="1" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="196">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="196" s="64">
       <c r="A196" s="1">
         <f>SUM(K196,M196,O196,Q196,S196,U196)</f>
         <v/>
@@ -30605,7 +30587,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Hot Fudge ($</t>
+          <t>Sales Tax (7%) $</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -30620,29 +30602,29 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Hot Fudge</t>
+          <t>Sales Tax</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Prepared Meals</t>
+          <t>Fees &amp; Charges</t>
         </is>
       </c>
       <c r="J196" s="2" t="n">
         <v>46274</v>
       </c>
       <c r="K196" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="197">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="197" s="64">
       <c r="A197" s="1">
         <f>SUM(K197,M197,O197,Q197,S197,U197)</f>
         <v/>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>SurfinTurtle</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -30652,44 +30634,44 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Arctic Cyclone</t>
+          <t>Chobani 20G Drk 4PK Straw</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Arctic Cyclone</t>
+          <t>Chobani Protein Greek Yogurt Drink, Strawberries &amp; Cream</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Prepared Meals</t>
+          <t>Yogurt</t>
         </is>
       </c>
       <c r="J197" s="2" t="n">
-        <v>46274</v>
+        <v>46278</v>
       </c>
       <c r="K197" s="1" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="198">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="198" s="64">
       <c r="A198" s="1">
         <f>SUM(K198,M198,O198,Q198,S198,U198)</f>
         <v/>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>SurfinTurtle</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -30699,37 +30681,37 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Sales Tax (7%) $</t>
+          <t>Meyers Hand Soap Lemon</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>T</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Sales Tax</t>
+          <t>Mrs. Meyer's Lemon Verbena Hand Soap</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Fees &amp; Charges</t>
+          <t>Hand Soap</t>
         </is>
       </c>
       <c r="J198" s="2" t="n">
-        <v>46274</v>
+        <v>46278</v>
       </c>
       <c r="K198" s="1" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="199">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="199" s="64">
       <c r="A199" s="1">
         <f>SUM(K199,M199,O199,Q199,S199,U199)</f>
         <v/>
@@ -30746,12 +30728,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Silk Soy Organic Nsa Hg</t>
+          <t>Tums Chwy Bites Brry 60ct</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -30761,52 +30743,22 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Silk Organic Unsweet Soymilk, Half Gallon</t>
+          <t>Tums Chewy Bites Berry, 60 Count</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Plant-Based Milk</t>
+          <t>Antacids</t>
         </is>
       </c>
       <c r="J199" s="2" t="n">
-        <v>46259</v>
+        <v>46278</v>
       </c>
       <c r="K199" s="1" t="n">
-        <v>6.19</v>
-      </c>
-      <c r="L199" s="2" t="n">
-        <v>46259</v>
-      </c>
-      <c r="M199" s="1" t="n">
-        <v>6.19</v>
-      </c>
-      <c r="N199" s="2" t="n">
-        <v>46259</v>
-      </c>
-      <c r="O199" s="1" t="n">
-        <v>6.19</v>
-      </c>
-      <c r="P199" s="2" t="n">
-        <v>46278</v>
-      </c>
-      <c r="Q199" s="1" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="R199" s="2" t="n">
-        <v>46299</v>
-      </c>
-      <c r="S199" s="1" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="T199" s="2" t="n">
-        <v>46299</v>
-      </c>
-      <c r="U199" s="1" t="n">
-        <v>6.79</v>
-      </c>
-    </row>
-    <row r="200">
+        <v>10.29</v>
+      </c>
+    </row>
+    <row r="200" s="64">
       <c r="A200" s="1">
         <f>SUM(K200,M200,O200,Q200,S200,U200)</f>
         <v/>
@@ -30823,12 +30775,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Chobani 20G Drk 4PK Straw</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>T</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -30838,29 +30790,31 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Chobani Protein Greek Yogurt Drink, Strawberries &amp; Cream</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Yogurt</t>
+          <t>Fees &amp; Charges</t>
         </is>
       </c>
       <c r="J200" s="2" t="n">
         <v>46278</v>
       </c>
-      <c r="K200" s="1" t="n">
-        <v>10.99</v>
-      </c>
-    </row>
-    <row r="201">
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" s="64">
       <c r="A201" s="1">
         <f>SUM(K201,M201,O201,Q201,S201,U201)</f>
         <v/>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -30870,44 +30824,44 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Meyers Hand Soap Lemon</t>
+          <t>Purina Tidy Cats Free and Clean Clumping Cat Litter</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Mrs. Meyer's Lemon Verbena Hand Soap</t>
+          <t>Purina Tidy Cats Free &amp; Clean Clumping Cat Litter</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Hand Soap</t>
+          <t>Cat Litter</t>
         </is>
       </c>
       <c r="J201" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K201" s="1" t="n">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="202">
+        <v>25.94</v>
+      </c>
+    </row>
+    <row r="202" s="64">
       <c r="A202" s="1">
         <f>SUM(K202,M202,O202,Q202,S202,U202)</f>
         <v/>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -30917,7 +30871,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Tums Chwy Bites Brry 60ct</t>
+          <t>Mott's No Sugar Added Applesauce</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -30927,34 +30881,34 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Tums Chewy Bites Berry, 60 Count</t>
+          <t>Mott's No Sugar Added Applesauce</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Antacids</t>
+          <t>Applesauce</t>
         </is>
       </c>
       <c r="J202" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K202" s="1" t="n">
-        <v>10.29</v>
-      </c>
-    </row>
-    <row r="203">
+        <v>7.97</v>
+      </c>
+    </row>
+    <row r="203" s="64">
       <c r="A203" s="1">
         <f>SUM(K203,M203,O203,Q203,S203,U203)</f>
         <v/>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -30964,39 +30918,37 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Giovanni Rana Tortellini</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Giovanni Rana Tortellini</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Fees &amp; Charges</t>
+          <t>Refrigerated Pasta</t>
         </is>
       </c>
       <c r="J203" s="2" t="n">
         <v>46278</v>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
+      <c r="K203" s="1" t="n">
+        <v>8.74</v>
+      </c>
+    </row>
+    <row r="204" s="64">
       <c r="A204" s="1">
         <f>SUM(K204,M204,O204,Q204,S204,U204)</f>
         <v/>
@@ -31013,7 +30965,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Purina Tidy Cats Free and Clean Clumping Cat Litter</t>
+          <t>Nature's Bakery Gluten Free Raspberry Fig Bars</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -31028,22 +30980,22 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Purina Tidy Cats Free &amp; Clean Clumping Cat Litter</t>
+          <t>Nature's Bakery Gluten-Free Raspberry Fig Bars</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Cat Litter</t>
+          <t>Snack Bars</t>
         </is>
       </c>
       <c r="J204" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K204" s="1" t="n">
-        <v>25.94</v>
-      </c>
-    </row>
-    <row r="205">
+        <v>5.97</v>
+      </c>
+    </row>
+    <row r="205" s="64">
       <c r="A205" s="1">
         <f>SUM(K205,M205,O205,Q205,S205,U205)</f>
         <v/>
@@ -31060,7 +31012,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Mott's No Sugar Added Applesauce</t>
+          <t>Tums Chewy Bites Ultra Strength Heartburn Relief Chews</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -31075,22 +31027,22 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Mott's No Sugar Added Applesauce</t>
+          <t>Tums Chewy Bites Ultra Strength Heartburn Relief Chews</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Applesauce</t>
+          <t>Antacids</t>
         </is>
       </c>
       <c r="J205" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K205" s="1" t="n">
-        <v>7.97</v>
-      </c>
-    </row>
-    <row r="206">
+        <v>11.96</v>
+      </c>
+    </row>
+    <row r="206" s="64">
       <c r="A206" s="1">
         <f>SUM(K206,M206,O206,Q206,S206,U206)</f>
         <v/>
@@ -31107,7 +31059,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Giovanni Rana Tortellini</t>
+          <t>Swiffer Sweep + Mop, Dry Pads Refill</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -31122,22 +31074,22 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Giovanni Rana Tortellini</t>
+          <t>Swiffer Sweep + Mop Dry Pads Refill</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Refrigerated Pasta</t>
+          <t>Household Cleaners</t>
         </is>
       </c>
       <c r="J206" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K206" s="1" t="n">
-        <v>8.74</v>
-      </c>
-    </row>
-    <row r="207">
+        <v>9.94</v>
+      </c>
+    </row>
+    <row r="207" s="64">
       <c r="A207" s="1">
         <f>SUM(K207,M207,O207,Q207,S207,U207)</f>
         <v/>
@@ -31154,7 +31106,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Nature's Bakery Gluten Free Raspberry Fig Bars</t>
+          <t>Fresh Mini Seedless Watermelon</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -31169,22 +31121,22 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Nature's Bakery Gluten-Free Raspberry Fig Bars</t>
+          <t>Mini Seedless Watermelon</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Snack Bars</t>
+          <t>Fresh Fruit</t>
         </is>
       </c>
       <c r="J207" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K207" s="1" t="n">
-        <v>5.97</v>
-      </c>
-    </row>
-    <row r="208">
+        <v>4.48</v>
+      </c>
+    </row>
+    <row r="208" s="64">
       <c r="A208" s="1">
         <f>SUM(K208,M208,O208,Q208,S208,U208)</f>
         <v/>
@@ -31201,7 +31153,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Tums Chewy Bites Ultra Strength Heartburn Relief Chews</t>
+          <t>Dave's Killer Bread Organic Oats &amp; Blues</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -31216,22 +31168,22 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Tums Chewy Bites Ultra Strength Heartburn Relief Chews</t>
+          <t>Dave's Killer Bread Organic Oats &amp; Blues</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Antacids</t>
+          <t>Bread</t>
         </is>
       </c>
       <c r="J208" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K208" s="1" t="n">
-        <v>11.96</v>
-      </c>
-    </row>
-    <row r="209">
+        <v>5.98</v>
+      </c>
+    </row>
+    <row r="209" s="64">
       <c r="A209" s="1">
         <f>SUM(K209,M209,O209,Q209,S209,U209)</f>
         <v/>
@@ -31248,7 +31200,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Swiffer Sweep + Mop, Dry Pads Refill</t>
+          <t>Chobani Low-Fat Vanilla Greek Yogurt Mixed Berry On The Bottom</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -31263,22 +31215,22 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Swiffer Sweep + Mop Dry Pads Refill</t>
+          <t>Chobani Vanilla Mixed Berry Greek Yogurt</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Household Cleaners</t>
+          <t>Yogurt</t>
         </is>
       </c>
       <c r="J209" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K209" s="1" t="n">
-        <v>9.94</v>
-      </c>
-    </row>
-    <row r="210">
+        <v>4.67</v>
+      </c>
+    </row>
+    <row r="210" s="64">
       <c r="A210" s="1">
         <f>SUM(K210,M210,O210,Q210,S210,U210)</f>
         <v/>
@@ -31295,7 +31247,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Fresh Mini Seedless Watermelon</t>
+          <t>Marketside Classic Italian Salad Kit</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -31310,22 +31262,22 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Mini Seedless Watermelon</t>
+          <t>Marketside Classic Italian Salad Kit</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Fresh Fruit</t>
+          <t>Salad Kits</t>
         </is>
       </c>
       <c r="J210" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K210" s="1" t="n">
-        <v>4.48</v>
-      </c>
-    </row>
-    <row r="211">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="211" s="64">
       <c r="A211" s="1">
         <f>SUM(K211,M211,O211,Q211,S211,U211)</f>
         <v/>
@@ -31342,7 +31294,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Dave's Killer Bread Organic Oats &amp; Blues</t>
+          <t>Fresh Express Avocado Twisted Caesar Chopped Salad Kit</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -31357,22 +31309,22 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Dave's Killer Bread Organic Oats &amp; Blues</t>
+          <t>Fresh Express Avocado Twisted Caesar Chopped Salad Kit</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Bread</t>
+          <t>Salad Kits</t>
         </is>
       </c>
       <c r="J211" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K211" s="1" t="n">
-        <v>5.98</v>
-      </c>
-    </row>
-    <row r="212">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="212" s="64">
       <c r="A212" s="1">
         <f>SUM(K212,M212,O212,Q212,S212,U212)</f>
         <v/>
@@ -31389,7 +31341,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Chobani Low-Fat Vanilla Greek Yogurt Mixed Berry On The Bottom</t>
+          <t>Hunt's Tomato Paste</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -31404,22 +31356,22 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Chobani Vanilla Mixed Berry Greek Yogurt</t>
+          <t>Hunt's Tomato Paste</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Yogurt</t>
+          <t>Canned Tomatoes</t>
         </is>
       </c>
       <c r="J212" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K212" s="1" t="n">
-        <v>4.67</v>
-      </c>
-    </row>
-    <row r="213">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="213" s="64">
       <c r="A213" s="1">
         <f>SUM(K213,M213,O213,Q213,S213,U213)</f>
         <v/>
@@ -31436,7 +31388,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Marketside Classic Italian Salad Kit</t>
+          <t>Hunt's Crushed Tomatoes</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -31451,22 +31403,22 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Marketside Classic Italian Salad Kit</t>
+          <t>Hunt's Crushed Tomatoes</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>Salad Kits</t>
+          <t>Canned Tomatoes</t>
         </is>
       </c>
       <c r="J213" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K213" s="1" t="n">
-        <v>2.47</v>
-      </c>
-    </row>
-    <row r="214">
+        <v>2.22</v>
+      </c>
+    </row>
+    <row r="214" s="64">
       <c r="A214" s="1">
         <f>SUM(K214,M214,O214,Q214,S214,U214)</f>
         <v/>
@@ -31483,7 +31435,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Fresh Express Avocado Twisted Caesar Chopped Salad Kit</t>
+          <t>Great Value Heavy Whipping Cream</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -31498,22 +31450,22 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Fresh Express Avocado Twisted Caesar Chopped Salad Kit</t>
+          <t>Great Value Heavy Whipping Cream</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Salad Kits</t>
+          <t>Cream &amp; Half-and-Half</t>
         </is>
       </c>
       <c r="J214" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K214" s="1" t="n">
-        <v>3.98</v>
-      </c>
-    </row>
-    <row r="215">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="215" s="64">
       <c r="A215" s="1">
         <f>SUM(K215,M215,O215,Q215,S215,U215)</f>
         <v/>
@@ -31530,7 +31482,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Hunt's Tomato Paste</t>
+          <t>Marketside Fresh Baby Spinach</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -31545,22 +31497,22 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Hunt's Tomato Paste</t>
+          <t>Marketside Baby Spinach</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Canned Tomatoes</t>
+          <t>Fresh Vegetables</t>
         </is>
       </c>
       <c r="J215" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K215" s="1" t="n">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="216">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="216" s="64">
       <c r="A216" s="1">
         <f>SUM(K216,M216,O216,Q216,S216,U216)</f>
         <v/>
@@ -31577,7 +31529,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Hunt's Crushed Tomatoes</t>
+          <t>Hebrew National Bun Length Beef Franks</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -31592,22 +31544,22 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Hunt's Crushed Tomatoes</t>
+          <t>Hebrew National Bun Length Beef Franks</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Canned Tomatoes</t>
+          <t>Hot Dogs &amp; Sausages</t>
         </is>
       </c>
       <c r="J216" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K216" s="1" t="n">
-        <v>2.22</v>
-      </c>
-    </row>
-    <row r="217">
+        <v>5.74</v>
+      </c>
+    </row>
+    <row r="217" s="64">
       <c r="A217" s="1">
         <f>SUM(K217,M217,O217,Q217,S217,U217)</f>
         <v/>
@@ -31624,7 +31576,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Great Value Heavy Whipping Cream</t>
+          <t>Ball Park White Hot Dog Buns</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -31639,22 +31591,22 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Great Value Heavy Whipping Cream</t>
+          <t>Ball Park White Hot Dog Buns</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>Cream &amp; Half-and-Half</t>
+          <t>Bread</t>
         </is>
       </c>
       <c r="J217" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K217" s="1" t="n">
-        <v>2.96</v>
-      </c>
-    </row>
-    <row r="218">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="218" s="64">
       <c r="A218" s="1">
         <f>SUM(K218,M218,O218,Q218,S218,U218)</f>
         <v/>
@@ -31671,7 +31623,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Marketside Fresh Baby Spinach</t>
+          <t>Fresh Whole Green Onion</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -31686,7 +31638,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Marketside Baby Spinach</t>
+          <t>Green Onions</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -31698,10 +31650,10 @@
         <v>46278</v>
       </c>
       <c r="K218" s="1" t="n">
-        <v>2.18</v>
-      </c>
-    </row>
-    <row r="219">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="219" s="64">
       <c r="A219" s="1">
         <f>SUM(K219,M219,O219,Q219,S219,U219)</f>
         <v/>
@@ -31718,7 +31670,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Hebrew National Bun Length Beef Franks</t>
+          <t>Marketside Broccoli Florets</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -31733,22 +31685,22 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Hebrew National Bun Length Beef Franks</t>
+          <t>Marketside Broccoli Florets</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>Hot Dogs &amp; Sausages</t>
+          <t>Fresh Vegetables</t>
         </is>
       </c>
       <c r="J219" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K219" s="1" t="n">
-        <v>5.74</v>
-      </c>
-    </row>
-    <row r="220">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="220" s="64">
       <c r="A220" s="1">
         <f>SUM(K220,M220,O220,Q220,S220,U220)</f>
         <v/>
@@ -31765,7 +31717,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Ball Park White Hot Dog Buns</t>
+          <t>Great Value Large White Eggs</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -31780,22 +31732,22 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Ball Park White Hot Dog Buns</t>
+          <t>Great Value Large White Eggs</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Bread</t>
+          <t>Eggs</t>
         </is>
       </c>
       <c r="J220" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K220" s="1" t="n">
-        <v>3.27</v>
-      </c>
-    </row>
-    <row r="221">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="221" s="64">
       <c r="A221" s="1">
         <f>SUM(K221,M221,O221,Q221,S221,U221)</f>
         <v/>
@@ -31812,7 +31764,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Fresh Whole Green Onion</t>
+          <t>Organic Marketside Fresh Baby Peeled Carrots</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -31827,7 +31779,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Green Onions</t>
+          <t>Marketside Organic Baby Carrots</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -31839,10 +31791,10 @@
         <v>46278</v>
       </c>
       <c r="K221" s="1" t="n">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="222">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="222" s="64">
       <c r="A222" s="1">
         <f>SUM(K222,M222,O222,Q222,S222,U222)</f>
         <v/>
@@ -31859,7 +31811,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Marketside Broccoli Florets</t>
+          <t>Taylor Farms Everything Chopped Salad Kit</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -31874,22 +31826,22 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Marketside Broccoli Florets</t>
+          <t>Taylor Farms Everything Chopped Salad Kit</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Fresh Vegetables</t>
+          <t>Salad Kits</t>
         </is>
       </c>
       <c r="J222" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K222" s="1" t="n">
-        <v>2.47</v>
-      </c>
-    </row>
-    <row r="223">
+        <v>8.24</v>
+      </c>
+    </row>
+    <row r="223" s="64">
       <c r="A223" s="1">
         <f>SUM(K223,M223,O223,Q223,S223,U223)</f>
         <v/>
@@ -31906,7 +31858,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Great Value Large White Eggs</t>
+          <t>Mighty Sesame Fine Organic Sesame Tahini</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -31921,22 +31873,22 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Great Value Large White Eggs</t>
+          <t>Mighty Sesame Organic Tahini</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Eggs</t>
+          <t>Dips &amp; Spreads</t>
         </is>
       </c>
       <c r="J223" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K223" s="1" t="n">
-        <v>4.88</v>
-      </c>
-    </row>
-    <row r="224">
+        <v>5.78</v>
+      </c>
+    </row>
+    <row r="224" s="64">
       <c r="A224" s="1">
         <f>SUM(K224,M224,O224,Q224,S224,U224)</f>
         <v/>
@@ -31953,7 +31905,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Organic Marketside Fresh Baby Peeled Carrots</t>
+          <t>Tabatchnick Classic Wholesome Chicken Broth</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -31968,22 +31920,22 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Marketside Organic Baby Carrots</t>
+          <t>Tabatchnick Classic Chicken Broth</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Fresh Vegetables</t>
+          <t>Broth &amp; Stock</t>
         </is>
       </c>
       <c r="J224" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K224" s="1" t="n">
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="225">
+        <v>5.94</v>
+      </c>
+    </row>
+    <row r="225" s="64">
       <c r="A225" s="1">
         <f>SUM(K225,M225,O225,Q225,S225,U225)</f>
         <v/>
@@ -32000,7 +31952,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Taylor Farms Everything Chopped Salad Kit</t>
+          <t>Barilla Gluten Free Spaghetti Pasta</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -32015,22 +31967,22 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Taylor Farms Everything Chopped Salad Kit</t>
+          <t>Barilla Gluten-Free Spaghetti</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Salad Kits</t>
+          <t>Pasta</t>
         </is>
       </c>
       <c r="J225" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K225" s="1" t="n">
-        <v>8.24</v>
-      </c>
-    </row>
-    <row r="226">
+        <v>5.34</v>
+      </c>
+    </row>
+    <row r="226" s="64">
       <c r="A226" s="1">
         <f>SUM(K226,M226,O226,Q226,S226,U226)</f>
         <v/>
@@ -32047,7 +31999,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Mighty Sesame Fine Organic Sesame Tahini</t>
+          <t>Great Value Organic Smoked Paprika Seasoning</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -32062,22 +32014,22 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Mighty Sesame Organic Tahini</t>
+          <t>Great Value Organic Smoked Paprika</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Dips &amp; Spreads</t>
+          <t>Seasonings &amp; Spices</t>
         </is>
       </c>
       <c r="J226" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K226" s="1" t="n">
-        <v>5.78</v>
-      </c>
-    </row>
-    <row r="227">
+        <v>4.36</v>
+      </c>
+    </row>
+    <row r="227" s="64">
       <c r="A227" s="1">
         <f>SUM(K227,M227,O227,Q227,S227,U227)</f>
         <v/>
@@ -32094,7 +32046,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Tabatchnick Classic Wholesome Chicken Broth</t>
+          <t>Ocean Spray® Craisins®</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -32109,22 +32061,22 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Tabatchnick Classic Chicken Broth</t>
+          <t>Ocean Spray Craisins</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Broth &amp; Stock</t>
+          <t>Dried Fruit</t>
         </is>
       </c>
       <c r="J227" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K227" s="1" t="n">
-        <v>5.94</v>
-      </c>
-    </row>
-    <row r="228">
+        <v>3.97</v>
+      </c>
+    </row>
+    <row r="228" s="64">
       <c r="A228" s="1">
         <f>SUM(K228,M228,O228,Q228,S228,U228)</f>
         <v/>
@@ -32141,7 +32093,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Barilla Gluten Free Spaghetti Pasta</t>
+          <t>Kikkoman Teriyaki Marinade &amp; Sauce</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -32156,22 +32108,22 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Barilla Gluten-Free Spaghetti</t>
+          <t>Kikkoman Teriyaki Marinade &amp; Sauce</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Pasta</t>
+          <t>Sauces &amp; Condiments</t>
         </is>
       </c>
       <c r="J228" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K228" s="1" t="n">
-        <v>5.34</v>
-      </c>
-    </row>
-    <row r="229">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="229" s="64">
       <c r="A229" s="1">
         <f>SUM(K229,M229,O229,Q229,S229,U229)</f>
         <v/>
@@ -32188,7 +32140,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Great Value Organic Smoked Paprika Seasoning</t>
+          <t>Great Value 8.5 Inch Disposable Paper Plates</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -32203,22 +32155,22 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Great Value Organic Smoked Paprika</t>
+          <t>Great Value Paper Plates, 8.5 Inch</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Seasonings &amp; Spices</t>
+          <t>Disposable Tableware</t>
         </is>
       </c>
       <c r="J229" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K229" s="1" t="n">
-        <v>4.36</v>
-      </c>
-    </row>
-    <row r="230">
+        <v>5.58</v>
+      </c>
+    </row>
+    <row r="230" s="64">
       <c r="A230" s="1">
         <f>SUM(K230,M230,O230,Q230,S230,U230)</f>
         <v/>
@@ -32235,7 +32187,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Ocean Spray® Craisins®</t>
+          <t>Sterilite 6 Quart Small Storage Bin</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -32250,22 +32202,22 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Ocean Spray Craisins</t>
+          <t>Sterilite 6-Quart Storage Bin</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Dried Fruit</t>
+          <t>Storage &amp; Organization</t>
         </is>
       </c>
       <c r="J230" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K230" s="1" t="n">
-        <v>3.97</v>
-      </c>
-    </row>
-    <row r="231">
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="231" s="64">
       <c r="A231" s="1">
         <f>SUM(K231,M231,O231,Q231,S231,U231)</f>
         <v/>
@@ -32282,7 +32234,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Kikkoman Teriyaki Marinade &amp; Sauce</t>
+          <t>Mainstays 4 Pack Kitchen Scrubber Dishcloth Set</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -32297,22 +32249,22 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Kikkoman Teriyaki Marinade &amp; Sauce</t>
+          <t>Mainstays Kitchen Scrubber Dishcloth Set, 4-Pack</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Sauces &amp; Condiments</t>
+          <t>Dishwashing Supplies</t>
         </is>
       </c>
       <c r="J231" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K231" s="1" t="n">
-        <v>3.77</v>
-      </c>
-    </row>
-    <row r="232">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="232" s="64">
       <c r="A232" s="1">
         <f>SUM(K232,M232,O232,Q232,S232,U232)</f>
         <v/>
@@ -32329,7 +32281,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Great Value 8.5 Inch Disposable Paper Plates</t>
+          <t>Busch American Lager Beer</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -32344,22 +32296,22 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Great Value Paper Plates, 8.5 Inch</t>
+          <t>Busch American Lager Beer</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Disposable Tableware</t>
+          <t>Beer</t>
         </is>
       </c>
       <c r="J232" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K232" s="1" t="n">
-        <v>5.58</v>
-      </c>
-    </row>
-    <row r="233">
+        <v>17.87</v>
+      </c>
+    </row>
+    <row r="233" s="64">
       <c r="A233" s="1">
         <f>SUM(K233,M233,O233,Q233,S233,U233)</f>
         <v/>
@@ -32376,7 +32328,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Sterilite 6 Quart Small Storage Bin</t>
+          <t>Great Value Half and Half</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -32391,22 +32343,22 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Sterilite 6-Quart Storage Bin</t>
+          <t>Great Value Half &amp; Half</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Storage &amp; Organization</t>
+          <t>Cream &amp; Half-and-Half</t>
         </is>
       </c>
       <c r="J233" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K233" s="1" t="n">
-        <v>2.56</v>
-      </c>
-    </row>
-    <row r="234">
+        <v>9.84</v>
+      </c>
+    </row>
+    <row r="234" s="64">
       <c r="A234" s="1">
         <f>SUM(K234,M234,O234,Q234,S234,U234)</f>
         <v/>
@@ -32423,7 +32375,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Mainstays 4 Pack Kitchen Scrubber Dishcloth Set</t>
+          <t>Birds Eye Steamfresh Sweet Peas</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -32438,22 +32390,22 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Mainstays Kitchen Scrubber Dishcloth Set, 4-Pack</t>
+          <t>Birds Eye Steamfresh Sweet Peas</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>Dishwashing Supplies</t>
+          <t>Frozen Vegetables</t>
         </is>
       </c>
       <c r="J234" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K234" s="1" t="n">
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="235">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="235" s="64">
       <c r="A235" s="1">
         <f>SUM(K235,M235,O235,Q235,S235,U235)</f>
         <v/>
@@ -32470,7 +32422,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Busch American Lager Beer</t>
+          <t>Spice World Fresh Peeled Garlic</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -32485,22 +32437,22 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Busch American Lager Beer</t>
+          <t>Spice World Fresh Peeled Garlic</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Beer</t>
+          <t>Fresh Vegetables</t>
         </is>
       </c>
       <c r="J235" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K235" s="1" t="n">
-        <v>17.87</v>
-      </c>
-    </row>
-    <row r="236">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="236" s="64">
       <c r="A236" s="1">
         <f>SUM(K236,M236,O236,Q236,S236,U236)</f>
         <v/>
@@ -32517,7 +32469,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Great Value Half and Half</t>
+          <t>Cracker Barrel Cracker Cuts Variety Pack Cheese Snacks</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -32532,22 +32484,22 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Great Value Half &amp; Half</t>
+          <t>Cracker Barrel Cracker Cuts Variety Pack</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Cream &amp; Half-and-Half</t>
+          <t>Cheese</t>
         </is>
       </c>
       <c r="J236" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K236" s="1" t="n">
-        <v>9.84</v>
-      </c>
-    </row>
-    <row r="237">
+        <v>8.48</v>
+      </c>
+    </row>
+    <row r="237" s="64">
       <c r="A237" s="1">
         <f>SUM(K237,M237,O237,Q237,S237,U237)</f>
         <v/>
@@ -32564,7 +32516,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Birds Eye Steamfresh Sweet Peas</t>
+          <t>Fresh Pink Lady Apples</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -32579,22 +32531,22 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Birds Eye Steamfresh Sweet Peas</t>
+          <t>Pink Lady Apples</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>Frozen Vegetables</t>
+          <t>Fresh Fruit</t>
         </is>
       </c>
       <c r="J237" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K237" s="1" t="n">
-        <v>1.27</v>
-      </c>
-    </row>
-    <row r="238">
+        <v>4.97</v>
+      </c>
+    </row>
+    <row r="238" s="64">
       <c r="A238" s="1">
         <f>SUM(K238,M238,O238,Q238,S238,U238)</f>
         <v/>
@@ -32611,7 +32563,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Spice World Fresh Peeled Garlic</t>
+          <t>Fresh Whole Red Potatoes</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -32626,7 +32578,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Spice World Fresh Peeled Garlic</t>
+          <t>Red Potatoes</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -32638,10 +32590,10 @@
         <v>46278</v>
       </c>
       <c r="K238" s="1" t="n">
-        <v>3.07</v>
-      </c>
-    </row>
-    <row r="239">
+        <v>5.23</v>
+      </c>
+    </row>
+    <row r="239" s="64">
       <c r="A239" s="1">
         <f>SUM(K239,M239,O239,Q239,S239,U239)</f>
         <v/>
@@ -32658,7 +32610,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Cracker Barrel Cracker Cuts Variety Pack Cheese Snacks</t>
+          <t>Fresh Blueberries</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -32673,22 +32625,22 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Cracker Barrel Cracker Cuts Variety Pack</t>
+          <t>Blueberries</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Cheese</t>
+          <t>Fresh Fruit</t>
         </is>
       </c>
       <c r="J239" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K239" s="1" t="n">
-        <v>8.48</v>
-      </c>
-    </row>
-    <row r="240">
+        <v>4.67</v>
+      </c>
+    </row>
+    <row r="240" s="64">
       <c r="A240" s="1">
         <f>SUM(K240,M240,O240,Q240,S240,U240)</f>
         <v/>
@@ -32705,7 +32657,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Fresh Pink Lady Apples</t>
+          <t>Fresh Bell Peppers</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -32720,22 +32672,22 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Pink Lady Apples</t>
+          <t>Bell Peppers</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>Fresh Fruit</t>
+          <t>Fresh Vegetables</t>
         </is>
       </c>
       <c r="J240" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K240" s="1" t="n">
-        <v>4.97</v>
-      </c>
-    </row>
-    <row r="241">
+        <v>2.97</v>
+      </c>
+    </row>
+    <row r="241" s="64">
       <c r="A241" s="1">
         <f>SUM(K241,M241,O241,Q241,S241,U241)</f>
         <v/>
@@ -32752,7 +32704,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Fresh Whole Red Potatoes</t>
+          <t>Fresh Pears Bartlett Bulk</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -32767,22 +32719,22 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Red Potatoes</t>
+          <t>Bartlett Pears</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Fresh Vegetables</t>
+          <t>Fresh Fruit</t>
         </is>
       </c>
       <c r="J241" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K241" s="1" t="n">
-        <v>5.23</v>
-      </c>
-    </row>
-    <row r="242">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="242" s="64">
       <c r="A242" s="1">
         <f>SUM(K242,M242,O242,Q242,S242,U242)</f>
         <v/>
@@ -32799,7 +32751,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Fresh Blueberries</t>
+          <t>Fresh Tomato on the Vine</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -32814,22 +32766,22 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Blueberries</t>
+          <t>Tomatoes on the Vine</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Fresh Fruit</t>
+          <t>Fresh Vegetables</t>
         </is>
       </c>
       <c r="J242" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K242" s="1" t="n">
-        <v>4.67</v>
-      </c>
-    </row>
-    <row r="243">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="243" s="64">
       <c r="A243" s="1">
         <f>SUM(K243,M243,O243,Q243,S243,U243)</f>
         <v/>
@@ -32846,7 +32798,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Fresh Bell Peppers</t>
+          <t>Fresh Whole Sweet Onion</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -32861,7 +32813,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Bell Peppers</t>
+          <t>Sweet Onion</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -32873,10 +32825,10 @@
         <v>46278</v>
       </c>
       <c r="K243" s="1" t="n">
-        <v>2.97</v>
-      </c>
-    </row>
-    <row r="244">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="244" s="64">
       <c r="A244" s="1">
         <f>SUM(K244,M244,O244,Q244,S244,U244)</f>
         <v/>
@@ -32893,7 +32845,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Fresh Pears Bartlett Bulk</t>
+          <t>Fresh Whole Red Onion</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -32908,22 +32860,22 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Bartlett Pears</t>
+          <t>Red Onion</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Fresh Fruit</t>
+          <t>Fresh Vegetables</t>
         </is>
       </c>
       <c r="J244" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K244" s="1" t="n">
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="245">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="245" s="64">
       <c r="A245" s="1">
         <f>SUM(K245,M245,O245,Q245,S245,U245)</f>
         <v/>
@@ -32940,7 +32892,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Fresh Tomato on the Vine</t>
+          <t>Fresh Banana</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -32955,22 +32907,22 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Tomatoes on the Vine</t>
+          <t>Bananas</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Fresh Vegetables</t>
+          <t>Fresh Fruit</t>
         </is>
       </c>
       <c r="J245" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K245" s="1" t="n">
-        <v>3.27</v>
-      </c>
-    </row>
-    <row r="246">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="246" s="64">
       <c r="A246" s="1">
         <f>SUM(K246,M246,O246,Q246,S246,U246)</f>
         <v/>
@@ -32987,7 +32939,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Fresh Whole Sweet Onion</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -33002,22 +32954,22 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Sweet Onion</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>Fresh Vegetables</t>
+          <t>Fees &amp; Charges</t>
         </is>
       </c>
       <c r="J246" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K246" s="1" t="n">
-        <v>0.91</v>
-      </c>
-    </row>
-    <row r="247">
+        <v>4.37</v>
+      </c>
+    </row>
+    <row r="247" s="64">
       <c r="A247" s="1">
         <f>SUM(K247,M247,O247,Q247,S247,U247)</f>
         <v/>
@@ -33034,7 +32986,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Fresh Whole Red Onion</t>
+          <t>Driver Tip</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -33049,22 +33001,22 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Red Onion</t>
+          <t>Driver Tip</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>Fresh Vegetables</t>
+          <t>Fees &amp; Charges</t>
         </is>
       </c>
       <c r="J247" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K247" s="1" t="n">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="248">
+        <v>22.11</v>
+      </c>
+    </row>
+    <row r="248" s="64">
       <c r="A248" s="1">
         <f>SUM(K248,M248,O248,Q248,S248,U248)</f>
         <v/>
@@ -33081,7 +33033,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Fresh Banana</t>
+          <t>Contribution</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -33096,29 +33048,29 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Bananas</t>
+          <t>Contribution</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Fresh Fruit</t>
+          <t>Contribution Shared Payment</t>
         </is>
       </c>
       <c r="J248" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="K248" s="1" t="n">
-        <v>2.15</v>
-      </c>
-    </row>
-    <row r="249">
+        <v>-144.14</v>
+      </c>
+    </row>
+    <row r="249" s="64">
       <c r="A249" s="1">
         <f>SUM(K249,M249,O249,Q249,S249,U249)</f>
         <v/>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>L3HAtriumCafe</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -33128,7 +33080,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Cage Free Scrambled Eggs</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -33143,29 +33095,29 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Cage-Free Scrambled Eggs</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Fees &amp; Charges</t>
+          <t>Prepared Meals</t>
         </is>
       </c>
       <c r="J249" s="2" t="n">
-        <v>46278</v>
+        <v>46282</v>
       </c>
       <c r="K249" s="1" t="n">
-        <v>4.37</v>
-      </c>
-    </row>
-    <row r="250">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="250" s="64">
       <c r="A250" s="1">
         <f>SUM(K250,M250,O250,Q250,S250,U250)</f>
         <v/>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -33175,44 +33127,44 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Driver Tip</t>
+          <t>Mogen David B1 Blackberry</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>T</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Driver Tip</t>
+          <t>Mogen David Blackberry Wine</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Fees &amp; Charges</t>
+          <t>Wine</t>
         </is>
       </c>
       <c r="J250" s="2" t="n">
-        <v>46278</v>
+        <v>46283</v>
       </c>
       <c r="K250" s="1" t="n">
-        <v>22.11</v>
-      </c>
-    </row>
-    <row r="251">
+        <v>7.19</v>
+      </c>
+    </row>
+    <row r="251" s="64">
       <c r="A251" s="1">
         <f>SUM(K251,M251,O251,Q251,S251,U251)</f>
         <v/>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>L3HAtriumCafe</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -33222,37 +33174,37 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Cage Free Scrambled Eggs</t>
+          <t>Bananas</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Cage-Free Scrambled Eggs</t>
+          <t>Bananas</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Prepared Meals</t>
+          <t>Fresh Fruit</t>
         </is>
       </c>
       <c r="J251" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="K251" s="1" t="n">
-        <v>2.59</v>
-      </c>
-    </row>
-    <row r="252">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="252" s="64">
       <c r="A252" s="1">
         <f>SUM(K252,M252,O252,Q252,S252,U252)</f>
         <v/>
@@ -33269,7 +33221,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Publix Half&amp;Half Hg</t>
+          <t>Gw Flourless Choc Truffle</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -33284,40 +33236,22 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Publix Half &amp; Half, Half Gallon</t>
+          <t>GreenWise Flourless Chocolate Truffle</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Cream &amp; Half-and-Half</t>
+          <t>Cakes &amp; Pies</t>
         </is>
       </c>
       <c r="J252" s="2" t="n">
-        <v>46259</v>
+        <v>46283</v>
       </c>
       <c r="K252" s="1" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="L252" s="2" t="n">
-        <v>46278</v>
-      </c>
-      <c r="M252" s="1" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="N252" s="2" t="n">
-        <v>46283</v>
-      </c>
-      <c r="O252" s="1" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="P252" s="2" t="n">
-        <v>46299</v>
-      </c>
-      <c r="Q252" s="1" t="n">
-        <v>5.89</v>
-      </c>
-    </row>
-    <row r="253">
+        <v>12.49</v>
+      </c>
+    </row>
+    <row r="253" s="64">
       <c r="A253" s="1">
         <f>SUM(K253,M253,O253,Q253,S253,U253)</f>
         <v/>
@@ -33334,12 +33268,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Mogen David B1 Blackberry</t>
+          <t>Pamp Swaddler Sz5 Bag</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -33349,22 +33283,22 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Mogen David Blackberry Wine</t>
+          <t>Pampers Swaddlers Size 5 Diapers</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Wine</t>
+          <t>Baby Care</t>
         </is>
       </c>
       <c r="J253" s="2" t="n">
         <v>46283</v>
       </c>
       <c r="K253" s="1" t="n">
-        <v>7.19</v>
-      </c>
-    </row>
-    <row r="254">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="254" s="64">
       <c r="A254" s="1">
         <f>SUM(K254,M254,O254,Q254,S254,U254)</f>
         <v/>
@@ -33381,7 +33315,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Bananas</t>
+          <t>Chobani 20G Drk</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -33396,22 +33330,22 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Bananas</t>
+          <t>Chobani Protein Greek Yogurt Drink</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Fresh Fruit</t>
+          <t>Yogurt</t>
         </is>
       </c>
       <c r="J254" s="2" t="n">
         <v>46283</v>
       </c>
       <c r="K254" s="1" t="n">
-        <v>1.72</v>
-      </c>
-    </row>
-    <row r="255">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="255" s="64">
       <c r="A255" s="1">
         <f>SUM(K255,M255,O255,Q255,S255,U255)</f>
         <v/>
@@ -33428,7 +33362,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Gw Flourless Choc Truffle</t>
+          <t>Mini Pumpkin Cc Pie</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -33443,7 +33377,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>GreenWise Flourless Chocolate Truffle</t>
+          <t>Mini Pumpkin Cream Cheese Pie</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -33455,10 +33389,10 @@
         <v>46283</v>
       </c>
       <c r="K255" s="1" t="n">
-        <v>12.49</v>
-      </c>
-    </row>
-    <row r="256">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="256" s="64">
       <c r="A256" s="1">
         <f>SUM(K256,M256,O256,Q256,S256,U256)</f>
         <v/>
@@ -33475,12 +33409,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Pamp Swaddler Sz5 Bag</t>
+          <t>18 Mylar Balloon</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>T</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -33490,22 +33424,22 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Pampers Swaddlers Size 5 Diapers</t>
+          <t>18-Inch Mylar Balloon</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Baby Care</t>
+          <t>Balloons</t>
         </is>
       </c>
       <c r="J256" s="2" t="n">
         <v>46283</v>
       </c>
       <c r="K256" s="1" t="n">
-        <v>12.99</v>
-      </c>
-    </row>
-    <row r="257">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="257" s="64">
       <c r="A257" s="1">
         <f>SUM(K257,M257,O257,Q257,S257,U257)</f>
         <v/>
@@ -33522,12 +33456,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Chobani 20G Drk</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>T</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -33537,22 +33471,22 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Chobani Protein Greek Yogurt Drink</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Yogurt</t>
+          <t>Fees &amp; Charges</t>
         </is>
       </c>
       <c r="J257" s="2" t="n">
         <v>46283</v>
       </c>
       <c r="K257" s="1" t="n">
-        <v>10.99</v>
-      </c>
-    </row>
-    <row r="258">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="258" s="64">
       <c r="A258" s="1">
         <f>SUM(K258,M258,O258,Q258,S258,U258)</f>
         <v/>
@@ -33569,7 +33503,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Mini Pumpkin Cc Pie</t>
+          <t>SB OAT BROWN SUGAR</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -33579,27 +33513,27 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Mini Pumpkin Cream Cheese Pie</t>
+          <t>Starbucks Oatmilk Brown Sugar Creamer</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Cakes &amp; Pies</t>
+          <t>Coffee Creamer</t>
         </is>
       </c>
       <c r="J258" s="2" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="K258" s="1" t="n">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="259">
+        <v>6.69</v>
+      </c>
+    </row>
+    <row r="259" s="64">
       <c r="A259" s="1">
         <f>SUM(K259,M259,O259,Q259,S259,U259)</f>
         <v/>
@@ -33616,37 +33550,43 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>18 Mylar Balloon</t>
+          <t>RANA CHEESE TORTEL</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>18-Inch Mylar Balloon</t>
+          <t>Giovanni Rana Cheese Tortellini</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>Balloons</t>
+          <t>Refrigerated Pasta</t>
         </is>
       </c>
       <c r="J259" s="2" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="K259" s="1" t="n">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="260">
+        <v>5</v>
+      </c>
+      <c r="L259" s="2" t="n">
+        <v>46284</v>
+      </c>
+      <c r="M259" s="1" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="260" s="64">
       <c r="A260" s="1">
         <f>SUM(K260,M260,O260,Q260,S260,U260)</f>
         <v/>
@@ -33663,37 +33603,43 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>PROG VEG BROTH</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Progresso Vegetable Broth</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>Fees &amp; Charges</t>
+          <t>Broth &amp; Stock</t>
         </is>
       </c>
       <c r="J260" s="2" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="K260" s="1" t="n">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="261">
+        <v>2.89</v>
+      </c>
+      <c r="L260" s="2" t="n">
+        <v>46284</v>
+      </c>
+      <c r="M260" s="1" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="261" s="64">
       <c r="A261" s="1">
         <f>SUM(K261,M261,O261,Q261,S261,U261)</f>
         <v/>
@@ -33710,7 +33656,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>SB OAT BROWN SUGAR</t>
+          <t>LSR EVL  SWT/SLT PN</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -33725,29 +33671,29 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Starbucks Oatmilk Brown Sugar Creamer</t>
+          <t>LesserEvil Sweet &amp; Salty Popcorn</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Coffee Creamer</t>
+          <t>Popcorn</t>
         </is>
       </c>
       <c r="J261" s="2" t="n">
         <v>46284</v>
       </c>
       <c r="K261" s="1" t="n">
-        <v>6.69</v>
-      </c>
-    </row>
-    <row r="262">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="262" s="64">
       <c r="A262" s="1">
         <f>SUM(K262,M262,O262,Q262,S262,U262)</f>
         <v/>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>Cosco</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -33757,43 +33703,37 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>RANA CHEESE TORTEL</t>
+          <t>Pampers Swaddlers Ultra Diapers Sizes</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>1688</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Giovanni Rana Cheese Tortellini</t>
+          <t>Pampers Swaddlers Diapers</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>Refrigerated Pasta</t>
+          <t>Baby Care</t>
         </is>
       </c>
       <c r="J262" s="2" t="n">
-        <v>46284</v>
-      </c>
-      <c r="K262" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="L262" s="2" t="n">
-        <v>46284</v>
-      </c>
-      <c r="M262" s="1" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="263">
+        <v>46285</v>
+      </c>
+      <c r="K262" t="n">
+        <v>46.79</v>
+      </c>
+    </row>
+    <row r="263" s="64">
       <c r="A263" s="1">
         <f>SUM(K263,M263,O263,Q263,S263,U263)</f>
         <v/>
@@ -33810,7 +33750,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>PROG VEG BROTH</t>
+          <t>Vans Waffle Blueberry Gf</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -33820,33 +33760,39 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>1688</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Progresso Vegetable Broth</t>
+          <t>Van's Gluten Free Blueberry Waffles</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>Broth &amp; Stock</t>
+          <t>Frozen Breakfast</t>
         </is>
       </c>
       <c r="J263" s="2" t="n">
-        <v>46284</v>
+        <v>46259</v>
       </c>
       <c r="K263" s="1" t="n">
-        <v>2.89</v>
+        <v>3.89</v>
       </c>
       <c r="L263" s="2" t="n">
-        <v>46284</v>
+        <v>46259</v>
       </c>
       <c r="M263" s="1" t="n">
-        <v>2.89</v>
-      </c>
-    </row>
-    <row r="264">
+        <v>3.89</v>
+      </c>
+      <c r="N263" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="O263" s="1" t="n">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="264" s="64">
       <c r="A264" s="1">
         <f>SUM(K264,M264,O264,Q264,S264,U264)</f>
         <v/>
@@ -33863,7 +33809,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>LSR EVL  SWT/SLT PN</t>
+          <t>Chobani 4Pk Hero Batch</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -33873,34 +33819,40 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>1688</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>LesserEvil Sweet &amp; Salty Popcorn</t>
+          <t>Chobani Greek Yogurt 4-Pack, Hero Batch</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>Popcorn</t>
+          <t>Yogurt</t>
         </is>
       </c>
       <c r="J264" s="2" t="n">
-        <v>46284</v>
+        <v>46259</v>
       </c>
       <c r="K264" s="1" t="n">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="265">
+        <v>5.65</v>
+      </c>
+      <c r="L264" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="M264" s="1" t="n">
+        <v>5.65</v>
+      </c>
+    </row>
+    <row r="265" s="64">
       <c r="A265" s="1">
         <f>SUM(K265,M265,O265,Q265,S265,U265)</f>
         <v/>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Cosco</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -33910,44 +33862,74 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Pampers Swaddlers Ultra Diapers Sizes</t>
+          <t>Silk Soy Organic Nsa Hg</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Pampers Swaddlers Diapers</t>
+          <t>Silk Organic Unsweet Soymilk, Half Gallon</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>Baby Care</t>
+          <t>Plant-Based Milk</t>
         </is>
       </c>
       <c r="J265" s="2" t="n">
-        <v>46285</v>
-      </c>
-      <c r="K265" t="n">
-        <v>46.79</v>
-      </c>
-    </row>
-    <row r="266">
+        <v>46259</v>
+      </c>
+      <c r="K265" s="1" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="L265" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="M265" s="1" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="N265" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="O265" s="1" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="P265" s="2" t="n">
+        <v>46278</v>
+      </c>
+      <c r="Q265" s="1" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="R265" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="S265" s="1" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="T265" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="U265" s="1" t="n">
+        <v>6.79</v>
+      </c>
+    </row>
+    <row r="266" s="64">
       <c r="A266" s="1">
         <f>SUM(K266,M266,O266,Q266,S266,U266)</f>
         <v/>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -33957,37 +33939,55 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Contribution</t>
+          <t>Publix Half&amp;Half Hg</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Contribution</t>
+          <t>Publix Half &amp; Half, Half Gallon</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>Contribution Shared Payment</t>
+          <t>Cream &amp; Half-and-Half</t>
         </is>
       </c>
       <c r="J266" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="K266" s="1" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="L266" s="2" t="n">
         <v>46278</v>
       </c>
-      <c r="K266" s="1" t="n">
-        <v>-144.14</v>
-      </c>
-    </row>
-    <row r="267">
+      <c r="M266" s="1" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="N266" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="O266" s="1" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="P266" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="Q266" s="1" t="n">
+        <v>5.89</v>
+      </c>
+    </row>
+    <row r="267" s="64">
       <c r="A267" s="1">
         <f>SUM(K267,M267,O267,Q267,S267,U267)</f>
         <v/>
@@ -34019,7 +34019,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Waffle</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -34034,7 +34034,7 @@
         <v>3.89</v>
       </c>
     </row>
-    <row r="268">
+    <row r="268" s="64">
       <c r="A268" s="1">
         <f>SUM(K268,M268,O268,Q268,S268,U268)</f>
         <v/>
@@ -34066,7 +34066,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Flour Bread</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -34081,7 +34081,7 @@
         <v>11.99</v>
       </c>
     </row>
-    <row r="269">
+    <row r="269" s="64">
       <c r="A269" s="1">
         <f>SUM(K269,M269,O269,Q269,S269,U269)</f>
         <v/>
@@ -34113,7 +34113,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Brownie</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -34128,7 +34128,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="270">
+    <row r="270" s="64">
       <c r="A270" s="1">
         <f>SUM(K270,M270,O270,Q270,S270,U270)</f>
         <v/>
@@ -34160,7 +34160,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Coriander</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -34175,7 +34175,7 @@
         <v>2.49</v>
       </c>
     </row>
-    <row r="271">
+    <row r="271" s="64">
       <c r="A271" s="1">
         <f>SUM(K271,M271,O271,Q271,S271,U271)</f>
         <v/>
@@ -34207,7 +34207,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Peanut Puffs</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -34222,7 +34222,7 @@
         <v>2.29</v>
       </c>
     </row>
-    <row r="272">
+    <row r="272" s="64">
       <c r="A272" s="1">
         <f>SUM(K272,M272,O272,Q272,S272,U272)</f>
         <v/>
@@ -34254,7 +34254,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Basil</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -52095,8 +52095,8 @@
       <c r="C30" s="2" t="n">
         <v>46299</v>
       </c>
-      <c r="D30" s="71" t="n">
-        <v>46299.75710116533</v>
+      <c r="D30" s="72" t="n">
+        <v>46299.75710116898</v>
       </c>
     </row>
   </sheetData>
